--- a/research/traditional_assets/database/data/tunisia/tunisia_diversified.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1648684342779273</v>
+        <v>0.1646593816265104</v>
       </c>
       <c r="C2">
-        <v>1593.186234439378</v>
+        <v>1583.632627540592</v>
       </c>
       <c r="D2">
-        <v>1548.986234439378</v>
+        <v>1551.710627540592</v>
       </c>
       <c r="E2">
-        <v>-736.6999999999999</v>
+        <v>-724.4219999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.278</v>
       </c>
       <c r="G2">
         <v>44.2</v>
@@ -1451,28 +1451,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6175834</v>
       </c>
       <c r="N2">
-        <v>223.6333333333334</v>
+        <v>223.0157499333334</v>
       </c>
       <c r="O2">
-        <v>33.54500000000001</v>
+        <v>33.45236249000001</v>
       </c>
       <c r="P2">
-        <v>190.0883333333334</v>
+        <v>189.5633874433334</v>
       </c>
       <c r="Q2">
-        <v>253.7883333333334</v>
+        <v>253.2633874433334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1648684342779273</v>
+        <v>0.1658907390166772</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7344600103638105</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>362.1103373784551</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1646593816265104</v>
+        <v>0.1644503289750935</v>
       </c>
       <c r="C3">
-        <v>1583.632627540592</v>
+        <v>1574.088620979306</v>
       </c>
       <c r="D3">
-        <v>1551.710627540592</v>
+        <v>1554.444620979306</v>
       </c>
       <c r="E3">
-        <v>-724.4219999999999</v>
+        <v>-712.1439999999999</v>
       </c>
       <c r="F3">
-        <v>12.278</v>
+        <v>24.556</v>
       </c>
       <c r="G3">
         <v>44.2</v>
@@ -1533,28 +1533,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M3">
-        <v>0.6175834</v>
+        <v>1.2351668</v>
       </c>
       <c r="N3">
-        <v>223.0157499333334</v>
+        <v>222.3981665333334</v>
       </c>
       <c r="O3">
-        <v>33.45236249000001</v>
+        <v>33.35972498</v>
       </c>
       <c r="P3">
-        <v>189.5633874433334</v>
+        <v>189.0384415533334</v>
       </c>
       <c r="Q3">
-        <v>253.2633874433334</v>
+        <v>252.7384415533334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1658907390166772</v>
+        <v>0.1669339071174424</v>
       </c>
       <c r="T3">
-        <v>0.7344600103638105</v>
+        <v>0.7408398966096</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>362.1103373784551</v>
+        <v>181.0551686892275</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1644503289750935</v>
+        <v>0.1642412763236766</v>
       </c>
       <c r="C4">
-        <v>1574.088620979306</v>
+        <v>1564.55426559023</v>
       </c>
       <c r="D4">
-        <v>1554.444620979306</v>
+        <v>1557.18826559023</v>
       </c>
       <c r="E4">
-        <v>-712.1439999999999</v>
+        <v>-699.866</v>
       </c>
       <c r="F4">
-        <v>24.556</v>
+        <v>36.834</v>
       </c>
       <c r="G4">
         <v>44.2</v>
@@ -1615,28 +1615,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M4">
-        <v>1.2351668</v>
+        <v>1.8527502</v>
       </c>
       <c r="N4">
-        <v>222.3981665333334</v>
+        <v>221.7805831333334</v>
       </c>
       <c r="O4">
-        <v>33.35972498</v>
+        <v>33.26708747000001</v>
       </c>
       <c r="P4">
-        <v>189.0384415533334</v>
+        <v>188.5134956633334</v>
       </c>
       <c r="Q4">
-        <v>252.7384415533334</v>
+        <v>252.2134956633334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1669339071174424</v>
+        <v>0.1679985838388419</v>
       </c>
       <c r="T4">
-        <v>0.7408398966096</v>
+        <v>0.7473513269016944</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>181.0551686892275</v>
+        <v>120.7034457928184</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1642412763236766</v>
+        <v>0.1640322236722597</v>
       </c>
       <c r="C5">
-        <v>1564.55426559023</v>
+        <v>1555.02961256761</v>
       </c>
       <c r="D5">
-        <v>1557.18826559023</v>
+        <v>1559.94161256761</v>
       </c>
       <c r="E5">
-        <v>-699.866</v>
+        <v>-687.588</v>
       </c>
       <c r="F5">
-        <v>36.834</v>
+        <v>49.112</v>
       </c>
       <c r="G5">
         <v>44.2</v>
@@ -1697,28 +1697,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M5">
-        <v>1.8527502</v>
+        <v>2.4703336</v>
       </c>
       <c r="N5">
-        <v>221.7805831333334</v>
+        <v>221.1629997333334</v>
       </c>
       <c r="O5">
-        <v>33.26708747000001</v>
+        <v>33.17444996</v>
       </c>
       <c r="P5">
-        <v>188.5134956633334</v>
+        <v>187.9885497733334</v>
       </c>
       <c r="Q5">
-        <v>252.2134956633334</v>
+        <v>251.6885497733334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1679985838388419</v>
+        <v>0.1690854413252706</v>
       </c>
       <c r="T5">
-        <v>0.7473513269016944</v>
+        <v>0.7539984119915408</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>120.7034457928184</v>
+        <v>90.52758434461377</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1640322236722597</v>
+        <v>0.1638231710208428</v>
       </c>
       <c r="C6">
-        <v>1555.02961256761</v>
+        <v>1545.514713468408</v>
       </c>
       <c r="D6">
-        <v>1559.94161256761</v>
+        <v>1562.704713468408</v>
       </c>
       <c r="E6">
-        <v>-687.588</v>
+        <v>-675.3099999999999</v>
       </c>
       <c r="F6">
-        <v>49.112</v>
+        <v>61.39</v>
       </c>
       <c r="G6">
         <v>44.2</v>
@@ -1779,28 +1779,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M6">
-        <v>2.4703336</v>
+        <v>3.087917</v>
       </c>
       <c r="N6">
-        <v>221.1629997333334</v>
+        <v>220.5454163333334</v>
       </c>
       <c r="O6">
-        <v>33.17444996</v>
+        <v>33.08181245000001</v>
       </c>
       <c r="P6">
-        <v>187.9885497733334</v>
+        <v>187.4636038833334</v>
       </c>
       <c r="Q6">
-        <v>251.6885497733334</v>
+        <v>251.1636038833334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1690854413252706</v>
+        <v>0.1701951800219398</v>
       </c>
       <c r="T6">
-        <v>0.7539984119915408</v>
+        <v>0.7607854357148577</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>90.52758434461377</v>
+        <v>72.42206747569102</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1638231710208428</v>
+        <v>0.1636141183694259</v>
       </c>
       <c r="C7">
-        <v>1545.514713468408</v>
+        <v>1536.009620215526</v>
       </c>
       <c r="D7">
-        <v>1562.704713468408</v>
+        <v>1565.477620215526</v>
       </c>
       <c r="E7">
-        <v>-675.3099999999999</v>
+        <v>-663.0319999999999</v>
       </c>
       <c r="F7">
-        <v>61.39</v>
+        <v>73.66800000000001</v>
       </c>
       <c r="G7">
         <v>44.2</v>
@@ -1861,28 +1861,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M7">
-        <v>3.087917</v>
+        <v>3.7055004</v>
       </c>
       <c r="N7">
-        <v>220.5454163333334</v>
+        <v>219.9278329333334</v>
       </c>
       <c r="O7">
-        <v>33.08181245000001</v>
+        <v>32.98917494000001</v>
       </c>
       <c r="P7">
-        <v>187.4636038833334</v>
+        <v>186.9386579933334</v>
       </c>
       <c r="Q7">
-        <v>251.1636038833334</v>
+        <v>250.6386579933334</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1701951800219398</v>
+        <v>0.1713285301802404</v>
       </c>
       <c r="T7">
-        <v>0.7607854357148577</v>
+        <v>0.767716864198245</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>72.42206747569102</v>
+        <v>60.35172289640918</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1636141183694259</v>
+        <v>0.1634050657180091</v>
       </c>
       <c r="C8">
-        <v>1536.009620215527</v>
+        <v>1526.51438510105</v>
       </c>
       <c r="D8">
-        <v>1565.477620215526</v>
+        <v>1568.26038510105</v>
       </c>
       <c r="E8">
-        <v>-663.0319999999999</v>
+        <v>-650.7539999999999</v>
       </c>
       <c r="F8">
-        <v>73.66799999999999</v>
+        <v>85.94599999999998</v>
       </c>
       <c r="G8">
         <v>44.2</v>
@@ -1943,28 +1943,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M8">
-        <v>3.7055004</v>
+        <v>4.323083799999999</v>
       </c>
       <c r="N8">
-        <v>219.9278329333334</v>
+        <v>219.3102495333334</v>
       </c>
       <c r="O8">
-        <v>32.98917494000001</v>
+        <v>32.89653743</v>
       </c>
       <c r="P8">
-        <v>186.9386579933334</v>
+        <v>186.4137121033334</v>
       </c>
       <c r="Q8">
-        <v>250.6386579933334</v>
+        <v>250.1137121033334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1713285301802404</v>
+        <v>0.1724862534602248</v>
       </c>
       <c r="T8">
-        <v>0.767716864198245</v>
+        <v>0.7747973556597698</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>60.35172289640919</v>
+        <v>51.73004819692216</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.163405065718009</v>
+        <v>0.1631960130665922</v>
       </c>
       <c r="C9">
-        <v>1526.514385101051</v>
+        <v>1517.029060789546</v>
       </c>
       <c r="D9">
-        <v>1568.260385101051</v>
+        <v>1571.053060789546</v>
       </c>
       <c r="E9">
-        <v>-650.7539999999999</v>
+        <v>-638.4759999999999</v>
       </c>
       <c r="F9">
-        <v>85.946</v>
+        <v>98.224</v>
       </c>
       <c r="G9">
         <v>44.2</v>
@@ -2025,28 +2025,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M9">
-        <v>4.3230838</v>
+        <v>4.9406672</v>
       </c>
       <c r="N9">
-        <v>219.3102495333334</v>
+        <v>218.6926661333334</v>
       </c>
       <c r="O9">
-        <v>32.89653743</v>
+        <v>32.80389992000001</v>
       </c>
       <c r="P9">
-        <v>186.4137121033334</v>
+        <v>185.8887662133334</v>
       </c>
       <c r="Q9">
-        <v>250.1137121033334</v>
+        <v>249.5887662133334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1724862534602248</v>
+        <v>0.1736691446376002</v>
       </c>
       <c r="T9">
-        <v>0.7747973556597698</v>
+        <v>0.7820317708487191</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.73004819692216</v>
+        <v>45.26379217230689</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1631960130665922</v>
+        <v>0.1629869604151753</v>
       </c>
       <c r="C10">
-        <v>1517.029060789546</v>
+        <v>1507.553700321377</v>
       </c>
       <c r="D10">
-        <v>1571.053060789546</v>
+        <v>1573.855700321377</v>
       </c>
       <c r="E10">
-        <v>-638.4759999999999</v>
+        <v>-626.198</v>
       </c>
       <c r="F10">
-        <v>98.224</v>
+        <v>110.502</v>
       </c>
       <c r="G10">
         <v>44.2</v>
@@ -2107,28 +2107,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M10">
-        <v>4.9406672</v>
+        <v>5.558250599999999</v>
       </c>
       <c r="N10">
-        <v>218.6926661333334</v>
+        <v>218.0750827333334</v>
       </c>
       <c r="O10">
-        <v>32.80389992000001</v>
+        <v>32.71126241</v>
       </c>
       <c r="P10">
-        <v>185.8887662133334</v>
+        <v>185.3638203233334</v>
       </c>
       <c r="Q10">
-        <v>249.5887662133334</v>
+        <v>249.0638203233333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1736691446376002</v>
+        <v>0.1748780334232695</v>
       </c>
       <c r="T10">
-        <v>0.7820317708487191</v>
+        <v>0.7894251841736891</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>45.26379217230689</v>
+        <v>40.23448193093946</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1629869604151753</v>
+        <v>0.1627779077637584</v>
       </c>
       <c r="C11">
-        <v>1507.553700321377</v>
+        <v>1498.088357116062</v>
       </c>
       <c r="D11">
-        <v>1573.855700321377</v>
+        <v>1576.668357116062</v>
       </c>
       <c r="E11">
-        <v>-626.198</v>
+        <v>-613.92</v>
       </c>
       <c r="F11">
-        <v>110.502</v>
+        <v>122.78</v>
       </c>
       <c r="G11">
         <v>44.2</v>
@@ -2189,28 +2189,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M11">
-        <v>5.558250599999999</v>
+        <v>6.175833999999999</v>
       </c>
       <c r="N11">
-        <v>218.0750827333334</v>
+        <v>217.4574993333334</v>
       </c>
       <c r="O11">
-        <v>32.71126241</v>
+        <v>32.61862490000001</v>
       </c>
       <c r="P11">
-        <v>185.3638203233334</v>
+        <v>184.8388744333334</v>
       </c>
       <c r="Q11">
-        <v>249.0638203233333</v>
+        <v>248.5388744333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1748780334232695</v>
+        <v>0.176113786404176</v>
       </c>
       <c r="T11">
-        <v>0.7894251841736891</v>
+        <v>0.7969828955725475</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.23448193093946</v>
+        <v>36.21103373784551</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1627779077637584</v>
+        <v>0.1625688551123415</v>
       </c>
       <c r="C12">
-        <v>1498.088357116062</v>
+        <v>1488.633084975671</v>
       </c>
       <c r="D12">
-        <v>1576.668357116062</v>
+        <v>1579.491084975671</v>
       </c>
       <c r="E12">
-        <v>-613.92</v>
+        <v>-601.6419999999999</v>
       </c>
       <c r="F12">
-        <v>122.78</v>
+        <v>135.058</v>
       </c>
       <c r="G12">
         <v>44.2</v>
@@ -2271,28 +2271,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M12">
-        <v>6.175834</v>
+        <v>6.793417399999999</v>
       </c>
       <c r="N12">
-        <v>217.4574993333334</v>
+        <v>216.8399159333334</v>
       </c>
       <c r="O12">
-        <v>32.61862490000001</v>
+        <v>32.52598739</v>
       </c>
       <c r="P12">
-        <v>184.8388744333334</v>
+        <v>184.3139285433334</v>
       </c>
       <c r="Q12">
-        <v>248.5388744333334</v>
+        <v>248.0139285433333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.176113786404176</v>
+        <v>0.1773773091149904</v>
       </c>
       <c r="T12">
-        <v>0.7969828955725475</v>
+        <v>0.8047104431826161</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.2110337378455</v>
+        <v>32.91912157985956</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1625688551123415</v>
+        <v>0.1623598024609246</v>
       </c>
       <c r="C13">
-        <v>1488.633084975671</v>
+        <v>1479.187938088254</v>
       </c>
       <c r="D13">
-        <v>1579.491084975671</v>
+        <v>1582.323938088254</v>
       </c>
       <c r="E13">
-        <v>-601.6419999999999</v>
+        <v>-589.3639999999999</v>
       </c>
       <c r="F13">
-        <v>135.058</v>
+        <v>147.336</v>
       </c>
       <c r="G13">
         <v>44.2</v>
@@ -2353,28 +2353,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M13">
-        <v>6.793417399999999</v>
+        <v>7.411000799999999</v>
       </c>
       <c r="N13">
-        <v>216.8399159333334</v>
+        <v>216.2223325333334</v>
       </c>
       <c r="O13">
-        <v>32.52598739</v>
+        <v>32.43334988</v>
       </c>
       <c r="P13">
-        <v>184.3139285433334</v>
+        <v>183.7889826533334</v>
       </c>
       <c r="Q13">
-        <v>248.0139285433333</v>
+        <v>247.4889826533334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1773773091149904</v>
+        <v>0.1786695482510507</v>
       </c>
       <c r="T13">
-        <v>0.8047104431826161</v>
+        <v>0.8126136168747318</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.91912157985956</v>
+        <v>30.17586144820459</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1623598024609246</v>
+        <v>0.1621507498095077</v>
       </c>
       <c r="C14">
-        <v>1479.187938088254</v>
+        <v>1469.752971031311</v>
       </c>
       <c r="D14">
-        <v>1582.323938088254</v>
+        <v>1585.166971031311</v>
       </c>
       <c r="E14">
-        <v>-589.3639999999999</v>
+        <v>-577.0859999999999</v>
       </c>
       <c r="F14">
-        <v>147.336</v>
+        <v>159.614</v>
       </c>
       <c r="G14">
         <v>44.2</v>
@@ -2435,28 +2435,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M14">
-        <v>7.411000799999999</v>
+        <v>8.028584199999999</v>
       </c>
       <c r="N14">
-        <v>216.2223325333334</v>
+        <v>215.6047491333334</v>
       </c>
       <c r="O14">
-        <v>32.43334988</v>
+        <v>32.34071237000001</v>
       </c>
       <c r="P14">
-        <v>183.7889826533334</v>
+        <v>183.2640367633334</v>
       </c>
       <c r="Q14">
-        <v>247.4889826533334</v>
+        <v>246.9640367633334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1786695482510507</v>
+        <v>0.1799914940339169</v>
       </c>
       <c r="T14">
-        <v>0.8126136168747318</v>
+        <v>0.8206984727206891</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.17586144820459</v>
+        <v>27.85464133680424</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1621507498095077</v>
+        <v>0.1619416971580908</v>
       </c>
       <c r="C15">
-        <v>1469.752971031311</v>
+        <v>1460.328238775293</v>
       </c>
       <c r="D15">
-        <v>1585.166971031311</v>
+        <v>1588.020238775293</v>
       </c>
       <c r="E15">
-        <v>-577.0859999999999</v>
+        <v>-564.808</v>
       </c>
       <c r="F15">
-        <v>159.614</v>
+        <v>171.892</v>
       </c>
       <c r="G15">
         <v>44.2</v>
@@ -2517,28 +2517,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M15">
-        <v>8.028584199999999</v>
+        <v>8.6461676</v>
       </c>
       <c r="N15">
-        <v>215.6047491333334</v>
+        <v>214.9871657333334</v>
       </c>
       <c r="O15">
-        <v>32.34071237000001</v>
+        <v>32.24807486</v>
       </c>
       <c r="P15">
-        <v>183.2640367633334</v>
+        <v>182.7390908733334</v>
       </c>
       <c r="Q15">
-        <v>246.9640367633334</v>
+        <v>246.4390908733334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1799914940339169</v>
+        <v>0.1813441827419661</v>
       </c>
       <c r="T15">
-        <v>0.8206984727206891</v>
+        <v>0.8289713484700407</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.85464133680424</v>
+        <v>25.86502409846108</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1619416971580908</v>
+        <v>0.1617326445066739</v>
       </c>
       <c r="C16">
-        <v>1460.328238775293</v>
+        <v>1450.913796687151</v>
       </c>
       <c r="D16">
-        <v>1588.020238775293</v>
+        <v>1590.883796687151</v>
       </c>
       <c r="E16">
-        <v>-564.808</v>
+        <v>-552.53</v>
       </c>
       <c r="F16">
-        <v>171.892</v>
+        <v>184.17</v>
       </c>
       <c r="G16">
         <v>44.2</v>
@@ -2599,28 +2599,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M16">
-        <v>8.6461676</v>
+        <v>9.263751000000001</v>
       </c>
       <c r="N16">
-        <v>214.9871657333334</v>
+        <v>214.3695823333334</v>
       </c>
       <c r="O16">
-        <v>32.24807486</v>
+        <v>32.15543735000001</v>
       </c>
       <c r="P16">
-        <v>182.7390908733334</v>
+        <v>182.2141449833334</v>
       </c>
       <c r="Q16">
-        <v>246.4390908733334</v>
+        <v>245.9141449833334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1813441827419661</v>
+        <v>0.1827286994196164</v>
       </c>
       <c r="T16">
-        <v>0.8289713484700407</v>
+        <v>0.8374388801193773</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.86502409846108</v>
+        <v>24.14068915856367</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1617326445066739</v>
+        <v>0.1615235918552571</v>
       </c>
       <c r="C17">
-        <v>1450.913796687151</v>
+        <v>1441.50970053391</v>
       </c>
       <c r="D17">
-        <v>1590.883796687151</v>
+        <v>1593.75770053391</v>
       </c>
       <c r="E17">
-        <v>-552.53</v>
+        <v>-540.252</v>
       </c>
       <c r="F17">
-        <v>184.17</v>
+        <v>196.448</v>
       </c>
       <c r="G17">
         <v>44.2</v>
@@ -2681,28 +2681,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M17">
-        <v>9.263750999999999</v>
+        <v>9.8813344</v>
       </c>
       <c r="N17">
-        <v>214.3695823333334</v>
+        <v>213.7519989333334</v>
       </c>
       <c r="O17">
-        <v>32.15543735000001</v>
+        <v>32.06279984</v>
       </c>
       <c r="P17">
-        <v>182.2141449833334</v>
+        <v>181.6891990933334</v>
       </c>
       <c r="Q17">
-        <v>245.9141449833334</v>
+        <v>245.3891990933334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1827286994196164</v>
+        <v>0.1841461807800679</v>
       </c>
       <c r="T17">
-        <v>0.8374388801193773</v>
+        <v>0.8461080196651266</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.14068915856367</v>
+        <v>22.63189608615344</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1615235918552571</v>
+        <v>0.1613145392038401</v>
       </c>
       <c r="C18">
-        <v>1441.50970053391</v>
+        <v>1432.116006486296</v>
       </c>
       <c r="D18">
-        <v>1593.75770053391</v>
+        <v>1596.642006486296</v>
       </c>
       <c r="E18">
-        <v>-540.252</v>
+        <v>-527.9739999999999</v>
       </c>
       <c r="F18">
-        <v>196.448</v>
+        <v>208.726</v>
       </c>
       <c r="G18">
         <v>44.2</v>
@@ -2763,28 +2763,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M18">
-        <v>9.8813344</v>
+        <v>10.4989178</v>
       </c>
       <c r="N18">
-        <v>213.7519989333334</v>
+        <v>213.1344155333334</v>
       </c>
       <c r="O18">
-        <v>32.06279984</v>
+        <v>31.97016233000001</v>
       </c>
       <c r="P18">
-        <v>181.6891990933334</v>
+        <v>181.1642532033334</v>
       </c>
       <c r="Q18">
-        <v>245.3891990933334</v>
+        <v>244.8642532033334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1841461807800679</v>
+        <v>0.1855978183178797</v>
       </c>
       <c r="T18">
-        <v>0.8461080196651266</v>
+        <v>0.8549860541396891</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.63189608615344</v>
+        <v>21.3006080810856</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1613145392038401</v>
+        <v>0.1611054865524232</v>
       </c>
       <c r="C19">
-        <v>1432.116006486296</v>
+        <v>1422.73277112239</v>
       </c>
       <c r="D19">
-        <v>1596.642006486296</v>
+        <v>1599.53677112239</v>
       </c>
       <c r="E19">
-        <v>-527.9739999999999</v>
+        <v>-515.6959999999999</v>
       </c>
       <c r="F19">
-        <v>208.726</v>
+        <v>221.004</v>
       </c>
       <c r="G19">
         <v>44.2</v>
@@ -2845,28 +2845,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M19">
-        <v>10.4989178</v>
+        <v>11.1165012</v>
       </c>
       <c r="N19">
-        <v>213.1344155333334</v>
+        <v>212.5168321333334</v>
       </c>
       <c r="O19">
-        <v>31.97016233000001</v>
+        <v>31.87752482000001</v>
       </c>
       <c r="P19">
-        <v>181.1642532033334</v>
+        <v>180.6393073133334</v>
       </c>
       <c r="Q19">
-        <v>244.8642532033334</v>
+        <v>244.3393073133334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1855978183178797</v>
+        <v>0.1870848616492966</v>
       </c>
       <c r="T19">
-        <v>0.8549860541396891</v>
+        <v>0.8640806260404603</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.3006080810856</v>
+        <v>20.11724096546973</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1611054865524233</v>
+        <v>0.1608964339010064</v>
       </c>
       <c r="C20">
-        <v>1422.73277112239</v>
+        <v>1413.360051431331</v>
       </c>
       <c r="D20">
-        <v>1599.536771122389</v>
+        <v>1602.442051431331</v>
       </c>
       <c r="E20">
-        <v>-515.6959999999999</v>
+        <v>-503.4179999999999</v>
       </c>
       <c r="F20">
-        <v>221.004</v>
+        <v>233.282</v>
       </c>
       <c r="G20">
         <v>44.2</v>
@@ -2927,28 +2927,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M20">
-        <v>11.1165012</v>
+        <v>11.7340846</v>
       </c>
       <c r="N20">
-        <v>212.5168321333334</v>
+        <v>211.8992487333334</v>
       </c>
       <c r="O20">
-        <v>31.87752482000001</v>
+        <v>31.78488731000001</v>
       </c>
       <c r="P20">
-        <v>180.6393073133334</v>
+        <v>180.1143614233334</v>
       </c>
       <c r="Q20">
-        <v>244.3393073133334</v>
+        <v>243.8143614233334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1870848616492966</v>
+        <v>0.1886086221000078</v>
       </c>
       <c r="T20">
-        <v>0.8640806260404603</v>
+        <v>0.8733997552721149</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.11724096546973</v>
+        <v>19.05843880939237</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1608964339010064</v>
+        <v>0.1606873812495895</v>
       </c>
       <c r="C21">
-        <v>1413.360051431331</v>
+        <v>1403.997904817055</v>
       </c>
       <c r="D21">
-        <v>1602.442051431331</v>
+        <v>1605.357904817055</v>
       </c>
       <c r="E21">
-        <v>-503.4179999999999</v>
+        <v>-491.1399999999999</v>
       </c>
       <c r="F21">
-        <v>233.282</v>
+        <v>245.56</v>
       </c>
       <c r="G21">
         <v>44.2</v>
@@ -3009,28 +3009,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M21">
-        <v>11.7340846</v>
+        <v>12.351668</v>
       </c>
       <c r="N21">
-        <v>211.8992487333334</v>
+        <v>211.2816653333334</v>
       </c>
       <c r="O21">
-        <v>31.78488731000001</v>
+        <v>31.69224980000001</v>
       </c>
       <c r="P21">
-        <v>180.1143614233334</v>
+        <v>179.5894155333334</v>
       </c>
       <c r="Q21">
-        <v>243.8143614233334</v>
+        <v>243.2894155333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1886086221000078</v>
+        <v>0.1901704765619869</v>
       </c>
       <c r="T21">
-        <v>0.8733997552721149</v>
+        <v>0.8829518627345608</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.05843880939237</v>
+        <v>18.10551686892276</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1606873812495895</v>
+        <v>0.1604783285981726</v>
       </c>
       <c r="C22">
-        <v>1403.997904817055</v>
+        <v>1394.646389102077</v>
       </c>
       <c r="D22">
-        <v>1605.357904817055</v>
+        <v>1608.284389102077</v>
       </c>
       <c r="E22">
-        <v>-491.1399999999999</v>
+        <v>-478.8619999999999</v>
       </c>
       <c r="F22">
-        <v>245.56</v>
+        <v>257.838</v>
       </c>
       <c r="G22">
         <v>44.2</v>
@@ -3091,28 +3091,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M22">
-        <v>12.351668</v>
+        <v>12.9692514</v>
       </c>
       <c r="N22">
-        <v>211.2816653333334</v>
+        <v>210.6640819333334</v>
       </c>
       <c r="O22">
-        <v>31.69224980000001</v>
+        <v>31.59961229000001</v>
       </c>
       <c r="P22">
-        <v>179.5894155333334</v>
+        <v>179.0644696433334</v>
       </c>
       <c r="Q22">
-        <v>243.2894155333334</v>
+        <v>242.7644696433334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1901704765619869</v>
+        <v>0.1917718716432564</v>
       </c>
       <c r="T22">
-        <v>0.8829518627345608</v>
+        <v>0.8927457957023852</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.10551686892276</v>
+        <v>17.24334939897405</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1604783285981726</v>
+        <v>0.1602692759467557</v>
       </c>
       <c r="C23">
-        <v>1394.646389102077</v>
+        <v>1385.305562531308</v>
       </c>
       <c r="D23">
-        <v>1608.284389102077</v>
+        <v>1611.221562531308</v>
       </c>
       <c r="E23">
-        <v>-478.862</v>
+        <v>-466.5839999999999</v>
       </c>
       <c r="F23">
-        <v>257.838</v>
+        <v>270.116</v>
       </c>
       <c r="G23">
         <v>44.2</v>
@@ -3173,28 +3173,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M23">
-        <v>12.9692514</v>
+        <v>13.5868348</v>
       </c>
       <c r="N23">
-        <v>210.6640819333334</v>
+        <v>210.0464985333334</v>
       </c>
       <c r="O23">
-        <v>31.59961229000001</v>
+        <v>31.50697478000001</v>
       </c>
       <c r="P23">
-        <v>179.0644696433334</v>
+        <v>178.5395237533334</v>
       </c>
       <c r="Q23">
-        <v>242.7644696433334</v>
+        <v>242.2395237533334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1917718716432564</v>
+        <v>0.1934143281368663</v>
       </c>
       <c r="T23">
-        <v>0.8927457957023851</v>
+        <v>0.902790855156564</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.24334939897406</v>
+        <v>16.45956078992978</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1602692759467557</v>
+        <v>0.1600602232953388</v>
       </c>
       <c r="C24">
-        <v>1385.305562531308</v>
+        <v>1375.975483775927</v>
       </c>
       <c r="D24">
-        <v>1611.221562531308</v>
+        <v>1614.169483775927</v>
       </c>
       <c r="E24">
-        <v>-466.5839999999999</v>
+        <v>-454.3059999999999</v>
       </c>
       <c r="F24">
-        <v>270.116</v>
+        <v>282.394</v>
       </c>
       <c r="G24">
         <v>44.2</v>
@@ -3255,28 +3255,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M24">
-        <v>13.5868348</v>
+        <v>14.2044182</v>
       </c>
       <c r="N24">
-        <v>210.0464985333334</v>
+        <v>209.4289151333334</v>
       </c>
       <c r="O24">
-        <v>31.50697478000001</v>
+        <v>31.41433727000001</v>
       </c>
       <c r="P24">
-        <v>178.5395237533334</v>
+        <v>178.0145778633334</v>
       </c>
       <c r="Q24">
-        <v>242.2395237533334</v>
+        <v>241.7145778633334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1934143281368663</v>
+        <v>0.1950994458381023</v>
       </c>
       <c r="T24">
-        <v>0.902790855156564</v>
+        <v>0.9130968252459162</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.45956078992978</v>
+        <v>15.74392771210674</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1600602232953388</v>
+        <v>0.1598511706439219</v>
       </c>
       <c r="C25">
-        <v>1375.975483775927</v>
+        <v>1366.656211937281</v>
       </c>
       <c r="D25">
-        <v>1614.169483775927</v>
+        <v>1617.128211937281</v>
       </c>
       <c r="E25">
-        <v>-454.3059999999999</v>
+        <v>-442.0279999999999</v>
       </c>
       <c r="F25">
-        <v>282.394</v>
+        <v>294.672</v>
       </c>
       <c r="G25">
         <v>44.2</v>
@@ -3337,28 +3337,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M25">
-        <v>14.2044182</v>
+        <v>14.8220016</v>
       </c>
       <c r="N25">
-        <v>209.4289151333334</v>
+        <v>208.8113317333334</v>
       </c>
       <c r="O25">
-        <v>31.41433727000001</v>
+        <v>31.32169976000001</v>
       </c>
       <c r="P25">
-        <v>178.0145778633334</v>
+        <v>177.4896319733334</v>
       </c>
       <c r="Q25">
-        <v>241.7145778633334</v>
+        <v>241.1896319733334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1950994458381023</v>
+        <v>0.1968289087420025</v>
       </c>
       <c r="T25">
-        <v>0.9130968252459162</v>
+        <v>0.923674005074462</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.74392771210674</v>
+        <v>15.0879307241023</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1598511706439219</v>
+        <v>0.159642117992505</v>
       </c>
       <c r="C26">
-        <v>1366.656211937281</v>
+        <v>1357.347806550839</v>
       </c>
       <c r="D26">
-        <v>1617.128211937281</v>
+        <v>1620.097806550839</v>
       </c>
       <c r="E26">
-        <v>-442.028</v>
+        <v>-429.7499999999999</v>
       </c>
       <c r="F26">
-        <v>294.672</v>
+        <v>306.95</v>
       </c>
       <c r="G26">
         <v>44.2</v>
@@ -3419,28 +3419,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M26">
-        <v>14.8220016</v>
+        <v>15.439585</v>
       </c>
       <c r="N26">
-        <v>208.8113317333334</v>
+        <v>208.1937483333334</v>
       </c>
       <c r="O26">
-        <v>31.32169976000001</v>
+        <v>31.22906225000001</v>
       </c>
       <c r="P26">
-        <v>177.4896319733334</v>
+        <v>176.9646860833334</v>
       </c>
       <c r="Q26">
-        <v>241.1896319733334</v>
+        <v>240.6646860833334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1968289087420025</v>
+        <v>0.1986044906566733</v>
       </c>
       <c r="T26">
-        <v>0.923674005074462</v>
+        <v>0.9345332430317688</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.0879307241023</v>
+        <v>14.4844134951382</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.159642117992505</v>
+        <v>0.1594330653410881</v>
       </c>
       <c r="C27">
-        <v>1357.347806550839</v>
+        <v>1348.050327590182</v>
       </c>
       <c r="D27">
-        <v>1620.097806550839</v>
+        <v>1623.078327590182</v>
       </c>
       <c r="E27">
-        <v>-429.7499999999999</v>
+        <v>-417.4719999999999</v>
       </c>
       <c r="F27">
-        <v>306.95</v>
+        <v>319.228</v>
       </c>
       <c r="G27">
         <v>44.2</v>
@@ -3501,28 +3501,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M27">
-        <v>15.439585</v>
+        <v>16.0571684</v>
       </c>
       <c r="N27">
-        <v>208.1937483333334</v>
+        <v>207.5761649333334</v>
       </c>
       <c r="O27">
-        <v>31.22906225000001</v>
+        <v>31.13642474000001</v>
       </c>
       <c r="P27">
-        <v>176.9646860833334</v>
+        <v>176.4397401933334</v>
       </c>
       <c r="Q27">
-        <v>240.6646860833334</v>
+        <v>240.1397401933334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1986044906566733</v>
+        <v>0.2004280612717407</v>
       </c>
       <c r="T27">
-        <v>0.9345332430317688</v>
+        <v>0.9456859739068408</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.4844134951382</v>
+        <v>13.92732066840212</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1594330653410881</v>
+        <v>0.1592240126896712</v>
       </c>
       <c r="C28">
-        <v>1348.050327590182</v>
+        <v>1338.763835471043</v>
       </c>
       <c r="D28">
-        <v>1623.078327590182</v>
+        <v>1626.069835471043</v>
       </c>
       <c r="E28">
-        <v>-417.4719999999999</v>
+        <v>-405.1939999999999</v>
       </c>
       <c r="F28">
-        <v>319.228</v>
+        <v>331.506</v>
       </c>
       <c r="G28">
         <v>44.2</v>
@@ -3583,28 +3583,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M28">
-        <v>16.0571684</v>
+        <v>16.6747518</v>
       </c>
       <c r="N28">
-        <v>207.5761649333334</v>
+        <v>206.9585815333334</v>
       </c>
       <c r="O28">
-        <v>31.13642474000001</v>
+        <v>31.04378723000001</v>
       </c>
       <c r="P28">
-        <v>176.4397401933334</v>
+        <v>175.9147943033334</v>
       </c>
       <c r="Q28">
-        <v>240.1397401933334</v>
+        <v>239.6147943033334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2004280612717407</v>
+        <v>0.202301592725577</v>
       </c>
       <c r="T28">
-        <v>0.9456859739068408</v>
+        <v>0.9571442590524629</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.92732066840212</v>
+        <v>13.41149397697982</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1592240126896712</v>
+        <v>0.1590149600382544</v>
       </c>
       <c r="C29">
-        <v>1338.763835471043</v>
+        <v>1329.488391055388</v>
       </c>
       <c r="D29">
-        <v>1626.069835471043</v>
+        <v>1629.072391055388</v>
       </c>
       <c r="E29">
-        <v>-405.1939999999999</v>
+        <v>-392.9159999999999</v>
       </c>
       <c r="F29">
-        <v>331.506</v>
+        <v>343.784</v>
       </c>
       <c r="G29">
         <v>44.2</v>
@@ -3665,28 +3665,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M29">
-        <v>16.6747518</v>
+        <v>17.2923352</v>
       </c>
       <c r="N29">
-        <v>206.9585815333334</v>
+        <v>206.3409981333334</v>
       </c>
       <c r="O29">
-        <v>31.04378723000001</v>
+        <v>30.95114972000001</v>
       </c>
       <c r="P29">
-        <v>175.9147943033334</v>
+        <v>175.3898484133334</v>
       </c>
       <c r="Q29">
-        <v>239.6147943033334</v>
+        <v>239.0898484133334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.202301592725577</v>
+        <v>0.2042271667197977</v>
       </c>
       <c r="T29">
-        <v>0.9571442590524629</v>
+        <v>0.9689208298965744</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.41149397697982</v>
+        <v>12.93251204923054</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1590149600382544</v>
+        <v>0.1591756573868374</v>
       </c>
       <c r="C30">
-        <v>1329.488391055388</v>
+        <v>1314.90136264553</v>
       </c>
       <c r="D30">
-        <v>1629.072391055388</v>
+        <v>1626.76336264553</v>
       </c>
       <c r="E30">
-        <v>-392.9159999999999</v>
+        <v>-380.6379999999999</v>
       </c>
       <c r="F30">
-        <v>343.784</v>
+        <v>356.062</v>
       </c>
       <c r="G30">
         <v>44.2</v>
@@ -3747,45 +3747,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M30">
-        <v>17.2923352</v>
+        <v>18.4440116</v>
       </c>
       <c r="N30">
-        <v>206.3409981333334</v>
+        <v>205.1893217333334</v>
       </c>
       <c r="O30">
-        <v>30.95114972000001</v>
+        <v>30.77839826</v>
       </c>
       <c r="P30">
-        <v>175.3898484133334</v>
+        <v>174.4109234733334</v>
       </c>
       <c r="Q30">
-        <v>239.0898484133334</v>
+        <v>238.1109234733333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2042271667197977</v>
+        <v>0.2062069822349824</v>
       </c>
       <c r="T30">
-        <v>0.9689208298965744</v>
+        <v>0.9810291351306607</v>
       </c>
       <c r="U30">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>12.93251204923054</v>
+        <v>12.124983337862</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1591756573868374</v>
+        <v>0.1589793547354205</v>
       </c>
       <c r="C31">
-        <v>1314.90136264553</v>
+        <v>1305.444883956212</v>
       </c>
       <c r="D31">
-        <v>1626.76336264553</v>
+        <v>1629.584883956212</v>
       </c>
       <c r="E31">
-        <v>-380.638</v>
+        <v>-368.36</v>
       </c>
       <c r="F31">
-        <v>356.062</v>
+        <v>368.34</v>
       </c>
       <c r="G31">
         <v>44.2</v>
@@ -3829,28 +3829,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M31">
-        <v>18.4440116</v>
+        <v>19.080012</v>
       </c>
       <c r="N31">
-        <v>205.1893217333334</v>
+        <v>204.5533213333334</v>
       </c>
       <c r="O31">
-        <v>30.77839826</v>
+        <v>30.6829982</v>
       </c>
       <c r="P31">
-        <v>174.4109234733334</v>
+        <v>173.8703231333334</v>
       </c>
       <c r="Q31">
-        <v>238.1109234733333</v>
+        <v>237.5703231333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2062069822349824</v>
+        <v>0.2082433639077437</v>
       </c>
       <c r="T31">
-        <v>0.9810291351306607</v>
+        <v>0.9934833919428638</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.124983337862</v>
+        <v>11.72081722659993</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1589793547354205</v>
+        <v>0.1587830520840036</v>
       </c>
       <c r="C32">
-        <v>1305.444883956212</v>
+        <v>1295.998209783661</v>
       </c>
       <c r="D32">
-        <v>1629.584883956212</v>
+        <v>1632.416209783661</v>
       </c>
       <c r="E32">
-        <v>-368.36</v>
+        <v>-356.0819999999999</v>
       </c>
       <c r="F32">
-        <v>368.34</v>
+        <v>380.618</v>
       </c>
       <c r="G32">
         <v>44.2</v>
@@ -3911,28 +3911,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M32">
-        <v>19.080012</v>
+        <v>19.7160124</v>
       </c>
       <c r="N32">
-        <v>204.5533213333334</v>
+        <v>203.9173209333334</v>
       </c>
       <c r="O32">
-        <v>30.6829982</v>
+        <v>30.58759814</v>
       </c>
       <c r="P32">
-        <v>173.8703231333334</v>
+        <v>173.3297227933334</v>
       </c>
       <c r="Q32">
-        <v>237.5703231333334</v>
+        <v>237.0297227933333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2082433639077437</v>
+        <v>0.2103387711362372</v>
       </c>
       <c r="T32">
-        <v>0.9934833919428638</v>
+        <v>1.006298641706145</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.72081722659993</v>
+        <v>11.34272634832251</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1587830520840036</v>
+        <v>0.1585867494325868</v>
       </c>
       <c r="C33">
-        <v>1295.998209783661</v>
+        <v>1286.561391321462</v>
       </c>
       <c r="D33">
-        <v>1632.416209783661</v>
+        <v>1635.257391321462</v>
       </c>
       <c r="E33">
-        <v>-356.0819999999999</v>
+        <v>-343.8039999999999</v>
       </c>
       <c r="F33">
-        <v>380.618</v>
+        <v>392.896</v>
       </c>
       <c r="G33">
         <v>44.2</v>
@@ -3993,28 +3993,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M33">
-        <v>19.7160124</v>
+        <v>20.3520128</v>
       </c>
       <c r="N33">
-        <v>203.9173209333334</v>
+        <v>203.2813205333334</v>
       </c>
       <c r="O33">
-        <v>30.58759814</v>
+        <v>30.49219808</v>
       </c>
       <c r="P33">
-        <v>173.3297227933334</v>
+        <v>172.7891224533334</v>
       </c>
       <c r="Q33">
-        <v>237.0297227933333</v>
+        <v>236.4891224533334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2103387711362372</v>
+        <v>0.2124958079890982</v>
       </c>
       <c r="T33">
-        <v>1.006298641706145</v>
+        <v>1.019490810580111</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.34272634832251</v>
+        <v>10.98826614993743</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1585867494325868</v>
+        <v>0.1583904467811699</v>
       </c>
       <c r="C34">
-        <v>1286.561391321462</v>
+        <v>1277.134480120224</v>
       </c>
       <c r="D34">
-        <v>1635.257391321462</v>
+        <v>1638.108480120224</v>
       </c>
       <c r="E34">
-        <v>-343.8039999999999</v>
+        <v>-331.526</v>
       </c>
       <c r="F34">
-        <v>392.896</v>
+        <v>405.174</v>
       </c>
       <c r="G34">
         <v>44.2</v>
@@ -4075,28 +4075,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M34">
-        <v>20.3520128</v>
+        <v>20.9880132</v>
       </c>
       <c r="N34">
-        <v>203.2813205333334</v>
+        <v>202.6453201333334</v>
       </c>
       <c r="O34">
-        <v>30.49219808</v>
+        <v>30.39679802000001</v>
       </c>
       <c r="P34">
-        <v>172.7891224533334</v>
+        <v>172.2485221133334</v>
       </c>
       <c r="Q34">
-        <v>236.4891224533334</v>
+        <v>235.9485221133334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2124958079890982</v>
+        <v>0.2147172340017461</v>
       </c>
       <c r="T34">
-        <v>1.019490810580111</v>
+        <v>1.033076775539868</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.98826614993743</v>
+        <v>10.65528838781812</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1583904467811699</v>
+        <v>0.158194144129753</v>
       </c>
       <c r="C35">
-        <v>1277.134480120224</v>
+        <v>1267.717528090703</v>
       </c>
       <c r="D35">
-        <v>1638.108480120224</v>
+        <v>1640.969528090703</v>
       </c>
       <c r="E35">
-        <v>-331.526</v>
+        <v>-319.2479999999999</v>
       </c>
       <c r="F35">
-        <v>405.174</v>
+        <v>417.452</v>
       </c>
       <c r="G35">
         <v>44.2</v>
@@ -4157,28 +4157,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M35">
-        <v>20.9880132</v>
+        <v>21.6240136</v>
       </c>
       <c r="N35">
-        <v>202.6453201333334</v>
+        <v>202.0093197333334</v>
       </c>
       <c r="O35">
-        <v>30.39679802000001</v>
+        <v>30.30139796</v>
       </c>
       <c r="P35">
-        <v>172.2485221133334</v>
+        <v>171.7079217733334</v>
       </c>
       <c r="Q35">
-        <v>235.9485221133334</v>
+        <v>235.4079217733334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2147172340017461</v>
+        <v>0.2170059759541712</v>
       </c>
       <c r="T35">
-        <v>1.033076775539868</v>
+        <v>1.047074436407496</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.65528838781812</v>
+        <v>10.34189755288229</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.158194144129753</v>
+        <v>0.1579978414783361</v>
       </c>
       <c r="C36">
-        <v>1267.717528090703</v>
+        <v>1258.310587506946</v>
       </c>
       <c r="D36">
-        <v>1640.969528090703</v>
+        <v>1643.840587506946</v>
       </c>
       <c r="E36">
-        <v>-319.2479999999999</v>
+        <v>-306.9699999999999</v>
       </c>
       <c r="F36">
-        <v>417.452</v>
+        <v>429.73</v>
       </c>
       <c r="G36">
         <v>44.2</v>
@@ -4239,28 +4239,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M36">
-        <v>21.6240136</v>
+        <v>22.260014</v>
       </c>
       <c r="N36">
-        <v>202.0093197333334</v>
+        <v>201.3733193333334</v>
       </c>
       <c r="O36">
-        <v>30.30139796</v>
+        <v>30.2059979</v>
       </c>
       <c r="P36">
-        <v>171.7079217733334</v>
+        <v>171.1673214333334</v>
       </c>
       <c r="Q36">
-        <v>235.4079217733334</v>
+        <v>234.8673214333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2170059759541712</v>
+        <v>0.2193651407359017</v>
       </c>
       <c r="T36">
-        <v>1.047074436407496</v>
+        <v>1.061502794532589</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.34189755288229</v>
+        <v>10.04641476565708</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1579978414783361</v>
+        <v>0.1583217388269192</v>
       </c>
       <c r="C37">
-        <v>1258.310587506946</v>
+        <v>1241.300740902569</v>
       </c>
       <c r="D37">
-        <v>1643.840587506946</v>
+        <v>1639.108740902569</v>
       </c>
       <c r="E37">
-        <v>-306.9699999999999</v>
+        <v>-294.6919999999999</v>
       </c>
       <c r="F37">
-        <v>429.73</v>
+        <v>442.008</v>
       </c>
       <c r="G37">
         <v>44.2</v>
@@ -4321,45 +4321,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M37">
-        <v>22.260014</v>
+        <v>23.647428</v>
       </c>
       <c r="N37">
-        <v>201.3733193333334</v>
+        <v>199.9859053333334</v>
       </c>
       <c r="O37">
-        <v>30.2059979</v>
+        <v>29.99788580000001</v>
       </c>
       <c r="P37">
-        <v>171.1673214333334</v>
+        <v>169.9880195333334</v>
       </c>
       <c r="Q37">
-        <v>234.8673214333334</v>
+        <v>233.6880195333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2193651407359017</v>
+        <v>0.2217980294170613</v>
       </c>
       <c r="T37">
-        <v>1.061502794532589</v>
+        <v>1.076382038849091</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.15</v>
       </c>
       <c r="W37">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>10.04641476565708</v>
+        <v>9.456983369748853</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1583217388269192</v>
+        <v>0.1581398861755023</v>
       </c>
       <c r="C38">
-        <v>1241.300740902568</v>
+        <v>1231.676084079613</v>
       </c>
       <c r="D38">
-        <v>1639.108740902568</v>
+        <v>1641.762084079613</v>
       </c>
       <c r="E38">
-        <v>-294.692</v>
+        <v>-282.4139999999999</v>
       </c>
       <c r="F38">
-        <v>442.008</v>
+        <v>454.286</v>
       </c>
       <c r="G38">
         <v>44.2</v>
@@ -4403,28 +4403,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M38">
-        <v>23.647428</v>
+        <v>24.304301</v>
       </c>
       <c r="N38">
-        <v>199.9859053333334</v>
+        <v>199.3290323333334</v>
       </c>
       <c r="O38">
-        <v>29.99788580000001</v>
+        <v>29.89935485000001</v>
       </c>
       <c r="P38">
-        <v>169.9880195333334</v>
+        <v>169.4296774833334</v>
       </c>
       <c r="Q38">
-        <v>233.6880195333334</v>
+        <v>233.1296774833334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2217980294170613</v>
+        <v>0.2243081526595275</v>
       </c>
       <c r="T38">
-        <v>1.076382038849091</v>
+        <v>1.091733640128022</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.456983369748855</v>
+        <v>9.201389224620506</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1581398861755023</v>
+        <v>0.1579580335240854</v>
       </c>
       <c r="C39">
-        <v>1231.676084079613</v>
+        <v>1222.060031499737</v>
       </c>
       <c r="D39">
-        <v>1641.762084079613</v>
+        <v>1644.424031499737</v>
       </c>
       <c r="E39">
-        <v>-282.4139999999999</v>
+        <v>-270.136</v>
       </c>
       <c r="F39">
-        <v>454.286</v>
+        <v>466.564</v>
       </c>
       <c r="G39">
         <v>44.2</v>
@@ -4485,28 +4485,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M39">
-        <v>24.304301</v>
+        <v>24.961174</v>
       </c>
       <c r="N39">
-        <v>199.3290323333334</v>
+        <v>198.6721593333334</v>
       </c>
       <c r="O39">
-        <v>29.89935485000001</v>
+        <v>29.8008239</v>
       </c>
       <c r="P39">
-        <v>169.4296774833334</v>
+        <v>168.8713354333334</v>
       </c>
       <c r="Q39">
-        <v>233.1296774833334</v>
+        <v>232.5713354333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2243081526595275</v>
+        <v>0.2268992476194926</v>
       </c>
       <c r="T39">
-        <v>1.091733640128022</v>
+        <v>1.107580454351434</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.201389224620506</v>
+        <v>8.959247402919967</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1579580335240854</v>
+        <v>0.1577761808726685</v>
       </c>
       <c r="C40">
-        <v>1222.060031499737</v>
+        <v>1212.452625083581</v>
       </c>
       <c r="D40">
-        <v>1644.424031499737</v>
+        <v>1647.094625083581</v>
       </c>
       <c r="E40">
-        <v>-270.136</v>
+        <v>-257.8579999999999</v>
       </c>
       <c r="F40">
-        <v>466.564</v>
+        <v>478.842</v>
       </c>
       <c r="G40">
         <v>44.2</v>
@@ -4567,28 +4567,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M40">
-        <v>24.961174</v>
+        <v>25.618047</v>
       </c>
       <c r="N40">
-        <v>198.6721593333334</v>
+        <v>198.0152863333334</v>
       </c>
       <c r="O40">
-        <v>29.8008239</v>
+        <v>29.70229295000001</v>
       </c>
       <c r="P40">
-        <v>168.8713354333334</v>
+        <v>168.3129933833334</v>
       </c>
       <c r="Q40">
-        <v>232.5713354333334</v>
+        <v>232.0129933833334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2268992476194926</v>
+        <v>0.2295752965125714</v>
       </c>
       <c r="T40">
-        <v>1.107580454351434</v>
+        <v>1.123946836254303</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.959247402919967</v>
+        <v>8.729523110537404</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1577761808726685</v>
+        <v>0.1575943282212517</v>
       </c>
       <c r="C41">
-        <v>1212.452625083581</v>
+        <v>1202.853907024549</v>
       </c>
       <c r="D41">
-        <v>1647.094625083581</v>
+        <v>1649.773907024549</v>
       </c>
       <c r="E41">
-        <v>-257.8579999999999</v>
+        <v>-245.5799999999999</v>
       </c>
       <c r="F41">
-        <v>478.842</v>
+        <v>491.12</v>
       </c>
       <c r="G41">
         <v>44.2</v>
@@ -4649,28 +4649,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M41">
-        <v>25.618047</v>
+        <v>26.27492</v>
       </c>
       <c r="N41">
-        <v>198.0152863333334</v>
+        <v>197.3584133333334</v>
       </c>
       <c r="O41">
-        <v>29.70229295000001</v>
+        <v>29.603762</v>
       </c>
       <c r="P41">
-        <v>168.3129933833334</v>
+        <v>167.7546513333334</v>
       </c>
       <c r="Q41">
-        <v>232.0129933833334</v>
+        <v>231.4546513333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2295752965125714</v>
+        <v>0.2323405470354195</v>
       </c>
       <c r="T41">
-        <v>1.123946836254303</v>
+        <v>1.140858764220601</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.729523110537404</v>
+        <v>8.511285032773969</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1575943282212517</v>
+        <v>0.1574124755698348</v>
       </c>
       <c r="C42">
-        <v>1202.853907024549</v>
+        <v>1193.263919791035</v>
       </c>
       <c r="D42">
-        <v>1649.773907024549</v>
+        <v>1652.461919791035</v>
       </c>
       <c r="E42">
-        <v>-245.5799999999999</v>
+        <v>-233.3019999999999</v>
       </c>
       <c r="F42">
-        <v>491.12</v>
+        <v>503.398</v>
       </c>
       <c r="G42">
         <v>44.2</v>
@@ -4731,28 +4731,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M42">
-        <v>26.27492</v>
+        <v>26.931793</v>
       </c>
       <c r="N42">
-        <v>197.3584133333334</v>
+        <v>196.7015403333334</v>
       </c>
       <c r="O42">
-        <v>29.603762</v>
+        <v>29.50523105000001</v>
       </c>
       <c r="P42">
-        <v>167.7546513333334</v>
+        <v>167.1963092833334</v>
       </c>
       <c r="Q42">
-        <v>231.4546513333333</v>
+        <v>230.8963092833334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2323405470354195</v>
+        <v>0.2351995348641268</v>
       </c>
       <c r="T42">
-        <v>1.140858764220601</v>
+        <v>1.158343977880672</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.511285032773969</v>
+        <v>8.30369271490143</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1574124755698348</v>
+        <v>0.1572306229184179</v>
       </c>
       <c r="C43">
-        <v>1193.263919791035</v>
+        <v>1183.682706128661</v>
       </c>
       <c r="D43">
-        <v>1652.461919791035</v>
+        <v>1655.158706128661</v>
       </c>
       <c r="E43">
-        <v>-233.3019999999999</v>
+        <v>-221.0239999999999</v>
       </c>
       <c r="F43">
-        <v>503.398</v>
+        <v>515.676</v>
       </c>
       <c r="G43">
         <v>44.2</v>
@@ -4813,28 +4813,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M43">
-        <v>26.931793</v>
+        <v>27.588666</v>
       </c>
       <c r="N43">
-        <v>196.7015403333334</v>
+        <v>196.0446673333334</v>
       </c>
       <c r="O43">
-        <v>29.50523105000001</v>
+        <v>29.40670010000001</v>
       </c>
       <c r="P43">
-        <v>167.1963092833334</v>
+        <v>166.6379672333334</v>
       </c>
       <c r="Q43">
-        <v>230.8963092833334</v>
+        <v>230.3379672333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2351995348641268</v>
+        <v>0.2381571084800308</v>
       </c>
       <c r="T43">
-        <v>1.158343977880672</v>
+        <v>1.176432129942814</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.30369271490143</v>
+        <v>8.105985745499016</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1572306229184179</v>
+        <v>0.157048770267001</v>
       </c>
       <c r="C44">
-        <v>1183.682706128661</v>
+        <v>1174.110309062543</v>
       </c>
       <c r="D44">
-        <v>1655.15870612866</v>
+        <v>1657.864309062543</v>
       </c>
       <c r="E44">
-        <v>-221.024</v>
+        <v>-208.746</v>
       </c>
       <c r="F44">
-        <v>515.6759999999999</v>
+        <v>527.954</v>
       </c>
       <c r="G44">
         <v>44.2</v>
@@ -4895,28 +4895,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M44">
-        <v>27.588666</v>
+        <v>28.245539</v>
       </c>
       <c r="N44">
-        <v>196.0446673333334</v>
+        <v>195.3877943333334</v>
       </c>
       <c r="O44">
-        <v>29.40670010000001</v>
+        <v>29.30816915</v>
       </c>
       <c r="P44">
-        <v>166.6379672333334</v>
+        <v>166.0796251833334</v>
       </c>
       <c r="Q44">
-        <v>230.3379672333334</v>
+        <v>229.7796251833334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2381571084800308</v>
+        <v>0.2412184566087737</v>
       </c>
       <c r="T44">
-        <v>1.176432129942813</v>
+        <v>1.195154954007136</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.105985745499019</v>
+        <v>7.917474449092063</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.157048770267001</v>
+        <v>0.1568669176155841</v>
       </c>
       <c r="C45">
-        <v>1174.110309062543</v>
+        <v>1164.546771899586</v>
       </c>
       <c r="D45">
-        <v>1657.864309062543</v>
+        <v>1660.578771899586</v>
       </c>
       <c r="E45">
-        <v>-208.746</v>
+        <v>-196.468</v>
       </c>
       <c r="F45">
-        <v>527.954</v>
+        <v>540.232</v>
       </c>
       <c r="G45">
         <v>44.2</v>
@@ -4977,28 +4977,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M45">
-        <v>28.245539</v>
+        <v>28.902412</v>
       </c>
       <c r="N45">
-        <v>195.3877943333334</v>
+        <v>194.7309213333334</v>
       </c>
       <c r="O45">
-        <v>29.30816915</v>
+        <v>29.20963820000001</v>
       </c>
       <c r="P45">
-        <v>166.0796251833334</v>
+        <v>165.5212831333334</v>
       </c>
       <c r="Q45">
-        <v>229.7796251833334</v>
+        <v>229.2212831333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2412184566087737</v>
+        <v>0.2443891385992573</v>
       </c>
       <c r="T45">
-        <v>1.195154954007136</v>
+        <v>1.214546450359469</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.917474449092063</v>
+        <v>7.737531847976335</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1568669176155841</v>
+        <v>0.1569910649641672</v>
       </c>
       <c r="C46">
-        <v>1164.546771899586</v>
+        <v>1150.414697997955</v>
       </c>
       <c r="D46">
-        <v>1660.578771899586</v>
+        <v>1658.724697997955</v>
       </c>
       <c r="E46">
-        <v>-196.468</v>
+        <v>-184.1899999999999</v>
       </c>
       <c r="F46">
-        <v>540.232</v>
+        <v>552.51</v>
       </c>
       <c r="G46">
         <v>44.2</v>
@@ -5059,45 +5059,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M46">
-        <v>28.902412</v>
+        <v>30.001293</v>
       </c>
       <c r="N46">
-        <v>194.7309213333334</v>
+        <v>193.6320403333334</v>
       </c>
       <c r="O46">
-        <v>29.20963820000001</v>
+        <v>29.04480605000001</v>
       </c>
       <c r="P46">
-        <v>165.5212831333334</v>
+        <v>164.5872342833334</v>
       </c>
       <c r="Q46">
-        <v>229.2212831333334</v>
+        <v>228.2872342833334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2443891385992573</v>
+        <v>0.2476751181166676</v>
       </c>
       <c r="T46">
-        <v>1.214546450359469</v>
+        <v>1.234643092033706</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.737531847976335</v>
+        <v>7.454123171735744</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1569910649641672</v>
+        <v>0.1568160123127503</v>
       </c>
       <c r="C47">
-        <v>1150.414697997955</v>
+        <v>1140.752213997009</v>
       </c>
       <c r="D47">
-        <v>1658.724697997955</v>
+        <v>1661.340213997009</v>
       </c>
       <c r="E47">
-        <v>-184.1899999999999</v>
+        <v>-171.9119999999999</v>
       </c>
       <c r="F47">
-        <v>552.51</v>
+        <v>564.788</v>
       </c>
       <c r="G47">
         <v>44.2</v>
@@ -5141,28 +5141,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M47">
-        <v>30.001293</v>
+        <v>30.6679884</v>
       </c>
       <c r="N47">
-        <v>193.6320403333334</v>
+        <v>192.9653449333334</v>
       </c>
       <c r="O47">
-        <v>29.04480605000001</v>
+        <v>28.94480174</v>
       </c>
       <c r="P47">
-        <v>164.5872342833334</v>
+        <v>164.0205431933334</v>
       </c>
       <c r="Q47">
-        <v>228.2872342833334</v>
+        <v>227.7205431933334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2476751181166676</v>
+        <v>0.2510828005791672</v>
       </c>
       <c r="T47">
-        <v>1.234643092033706</v>
+        <v>1.255484053769952</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.454123171735744</v>
+        <v>7.292077015828444</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1568160123127503</v>
+        <v>0.1566409596613335</v>
       </c>
       <c r="C48">
-        <v>1140.752213997009</v>
+        <v>1131.097991436813</v>
       </c>
       <c r="D48">
-        <v>1661.340213997009</v>
+        <v>1663.963991436813</v>
       </c>
       <c r="E48">
-        <v>-171.9119999999999</v>
+        <v>-159.6339999999999</v>
       </c>
       <c r="F48">
-        <v>564.788</v>
+        <v>577.066</v>
       </c>
       <c r="G48">
         <v>44.2</v>
@@ -5223,28 +5223,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M48">
-        <v>30.6679884</v>
+        <v>31.3346838</v>
       </c>
       <c r="N48">
-        <v>192.9653449333334</v>
+        <v>192.2986495333334</v>
       </c>
       <c r="O48">
-        <v>28.94480174</v>
+        <v>28.84479743000001</v>
       </c>
       <c r="P48">
-        <v>164.0205431933334</v>
+        <v>163.4538521033334</v>
       </c>
       <c r="Q48">
-        <v>227.7205431933334</v>
+        <v>227.1538521033334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2510828005791672</v>
+        <v>0.2546190748327046</v>
       </c>
       <c r="T48">
-        <v>1.255484053769952</v>
+        <v>1.277111466892471</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.292077015828444</v>
+        <v>7.136926441023585</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1566409596613335</v>
+        <v>0.1564659070099165</v>
       </c>
       <c r="C49">
-        <v>1131.097991436813</v>
+        <v>1121.452069521505</v>
       </c>
       <c r="D49">
-        <v>1663.963991436813</v>
+        <v>1666.596069521505</v>
       </c>
       <c r="E49">
-        <v>-159.6339999999999</v>
+        <v>-147.3559999999999</v>
       </c>
       <c r="F49">
-        <v>577.066</v>
+        <v>589.3440000000001</v>
       </c>
       <c r="G49">
         <v>44.2</v>
@@ -5305,28 +5305,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M49">
-        <v>31.3346838</v>
+        <v>32.0013792</v>
       </c>
       <c r="N49">
-        <v>192.2986495333334</v>
+        <v>191.6319541333334</v>
       </c>
       <c r="O49">
-        <v>28.84479743000001</v>
+        <v>28.74479312000001</v>
       </c>
       <c r="P49">
-        <v>163.4538521033334</v>
+        <v>162.8871610133334</v>
       </c>
       <c r="Q49">
-        <v>227.1538521033334</v>
+        <v>226.5871610133334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2546190748327046</v>
+        <v>0.2582913596344548</v>
       </c>
       <c r="T49">
-        <v>1.277111466892471</v>
+        <v>1.299570703596626</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.136926441023585</v>
+        <v>6.98824047350226</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1564659070099165</v>
+        <v>0.1562908543584996</v>
       </c>
       <c r="C50">
-        <v>1121.452069521505</v>
+        <v>1111.814487703666</v>
       </c>
       <c r="D50">
-        <v>1666.596069521505</v>
+        <v>1669.236487703666</v>
       </c>
       <c r="E50">
-        <v>-147.356</v>
+        <v>-135.078</v>
       </c>
       <c r="F50">
-        <v>589.3439999999999</v>
+        <v>601.622</v>
       </c>
       <c r="G50">
         <v>44.2</v>
@@ -5387,28 +5387,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M50">
-        <v>32.0013792</v>
+        <v>32.6680746</v>
       </c>
       <c r="N50">
-        <v>191.6319541333334</v>
+        <v>190.9652587333334</v>
       </c>
       <c r="O50">
-        <v>28.74479312000001</v>
+        <v>28.64478881</v>
       </c>
       <c r="P50">
-        <v>162.8871610133334</v>
+        <v>162.3204699233334</v>
       </c>
       <c r="Q50">
-        <v>226.5871610133334</v>
+        <v>226.0204699233334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2582913596344548</v>
+        <v>0.2621076556049012</v>
       </c>
       <c r="T50">
-        <v>1.299570703596626</v>
+        <v>1.322910694681335</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.988240473502261</v>
+        <v>6.845623320981806</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1562908543584996</v>
+        <v>0.1561158017070828</v>
       </c>
       <c r="C51">
-        <v>1111.814487703666</v>
+        <v>1102.185285686299</v>
       </c>
       <c r="D51">
-        <v>1669.236487703666</v>
+        <v>1671.885285686299</v>
       </c>
       <c r="E51">
-        <v>-135.078</v>
+        <v>-122.8</v>
       </c>
       <c r="F51">
-        <v>601.622</v>
+        <v>613.9</v>
       </c>
       <c r="G51">
         <v>44.2</v>
@@ -5469,28 +5469,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M51">
-        <v>32.6680746</v>
+        <v>33.33477</v>
       </c>
       <c r="N51">
-        <v>190.9652587333334</v>
+        <v>190.2985633333334</v>
       </c>
       <c r="O51">
-        <v>28.64478881</v>
+        <v>28.54478450000001</v>
       </c>
       <c r="P51">
-        <v>162.3204699233334</v>
+        <v>161.7537788333334</v>
       </c>
       <c r="Q51">
-        <v>226.0204699233334</v>
+        <v>225.4537788333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2621076556049012</v>
+        <v>0.2660766034141655</v>
       </c>
       <c r="T51">
-        <v>1.322910694681335</v>
+        <v>1.347184285409433</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.845623320981806</v>
+        <v>6.70871085456217</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1561158017070828</v>
+        <v>0.1559407490556659</v>
       </c>
       <c r="C52">
-        <v>1102.185285686299</v>
+        <v>1092.564503424816</v>
       </c>
       <c r="D52">
-        <v>1671.885285686299</v>
+        <v>1674.542503424816</v>
       </c>
       <c r="E52">
-        <v>-122.8</v>
+        <v>-110.5219999999999</v>
       </c>
       <c r="F52">
-        <v>613.9</v>
+        <v>626.178</v>
       </c>
       <c r="G52">
         <v>44.2</v>
@@ -5551,28 +5551,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M52">
-        <v>33.33477</v>
+        <v>34.0014654</v>
       </c>
       <c r="N52">
-        <v>190.2985633333334</v>
+        <v>189.6318679333334</v>
       </c>
       <c r="O52">
-        <v>28.54478450000001</v>
+        <v>28.44478019000001</v>
       </c>
       <c r="P52">
-        <v>161.7537788333334</v>
+        <v>161.1870877433334</v>
       </c>
       <c r="Q52">
-        <v>225.4537788333334</v>
+        <v>224.8870877433334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2660766034141655</v>
+        <v>0.2702075490931956</v>
       </c>
       <c r="T52">
-        <v>1.347184285409433</v>
+        <v>1.37244863494276</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.70871085456217</v>
+        <v>6.577167504472715</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1559407490556659</v>
+        <v>0.155765696404249</v>
       </c>
       <c r="C53">
-        <v>1092.564503424816</v>
+        <v>1082.952181129045</v>
       </c>
       <c r="D53">
-        <v>1674.542503424816</v>
+        <v>1677.208181129045</v>
       </c>
       <c r="E53">
-        <v>-110.5219999999999</v>
+        <v>-98.24399999999991</v>
       </c>
       <c r="F53">
-        <v>626.178</v>
+        <v>638.456</v>
       </c>
       <c r="G53">
         <v>44.2</v>
@@ -5633,28 +5633,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M53">
-        <v>34.0014654</v>
+        <v>34.6681608</v>
       </c>
       <c r="N53">
-        <v>189.6318679333334</v>
+        <v>188.9651725333334</v>
       </c>
       <c r="O53">
-        <v>28.44478019000001</v>
+        <v>28.34477588</v>
       </c>
       <c r="P53">
-        <v>161.1870877433334</v>
+        <v>160.6203966533334</v>
       </c>
       <c r="Q53">
-        <v>224.8870877433334</v>
+        <v>224.3203966533334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2702075490931956</v>
+        <v>0.274510617508852</v>
       </c>
       <c r="T53">
-        <v>1.37244863494276</v>
+        <v>1.398765665706641</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.577167504472715</v>
+        <v>6.450683514002086</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.155765696404249</v>
+        <v>0.155590643752832</v>
       </c>
       <c r="C54">
-        <v>1082.952181129045</v>
+        <v>1073.34835926526</v>
       </c>
       <c r="D54">
-        <v>1677.208181129045</v>
+        <v>1679.88235926526</v>
       </c>
       <c r="E54">
-        <v>-98.24399999999991</v>
+        <v>-85.96599999999989</v>
       </c>
       <c r="F54">
-        <v>638.456</v>
+        <v>650.734</v>
       </c>
       <c r="G54">
         <v>44.2</v>
@@ -5715,28 +5715,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M54">
-        <v>34.6681608</v>
+        <v>35.3348562</v>
       </c>
       <c r="N54">
-        <v>188.9651725333334</v>
+        <v>188.2984771333334</v>
       </c>
       <c r="O54">
-        <v>28.34477588</v>
+        <v>28.24477157000001</v>
       </c>
       <c r="P54">
-        <v>160.6203966533334</v>
+        <v>160.0537055633334</v>
       </c>
       <c r="Q54">
-        <v>224.3203966533334</v>
+        <v>223.7537055633334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.274510617508852</v>
+        <v>0.2789967952187916</v>
       </c>
       <c r="T54">
-        <v>1.398765665706641</v>
+        <v>1.42620257012005</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.450683514002086</v>
+        <v>6.328972504303933</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.155590643752832</v>
+        <v>0.1554155911014152</v>
       </c>
       <c r="C55">
-        <v>1073.34835926526</v>
+        <v>1063.753078558228</v>
       </c>
       <c r="D55">
-        <v>1679.88235926526</v>
+        <v>1682.565078558228</v>
       </c>
       <c r="E55">
-        <v>-85.96599999999989</v>
+        <v>-73.68799999999987</v>
       </c>
       <c r="F55">
-        <v>650.734</v>
+        <v>663.0120000000001</v>
       </c>
       <c r="G55">
         <v>44.2</v>
@@ -5797,28 +5797,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M55">
-        <v>35.3348562</v>
+        <v>36.00155160000001</v>
       </c>
       <c r="N55">
-        <v>188.2984771333334</v>
+        <v>187.6317817333334</v>
       </c>
       <c r="O55">
-        <v>28.24477157000001</v>
+        <v>28.14476726000001</v>
       </c>
       <c r="P55">
-        <v>160.0537055633334</v>
+        <v>159.4870144733334</v>
       </c>
       <c r="Q55">
-        <v>223.7537055633334</v>
+        <v>223.1870144733334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2789967952187916</v>
+        <v>0.2836780241335113</v>
       </c>
       <c r="T55">
-        <v>1.42620257012005</v>
+        <v>1.454832383420998</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.328972504303933</v>
+        <v>6.211769309779786</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1554155911014152</v>
+        <v>0.1557080384499983</v>
       </c>
       <c r="C56">
-        <v>1063.753078558228</v>
+        <v>1046.998047551376</v>
       </c>
       <c r="D56">
-        <v>1682.565078558228</v>
+        <v>1678.088047551376</v>
       </c>
       <c r="E56">
-        <v>-73.68799999999987</v>
+        <v>-61.40999999999985</v>
       </c>
       <c r="F56">
-        <v>663.0120000000001</v>
+        <v>675.2900000000001</v>
       </c>
       <c r="G56">
         <v>44.2</v>
@@ -5879,45 +5879,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M56">
-        <v>36.00155160000001</v>
+        <v>37.343537</v>
       </c>
       <c r="N56">
-        <v>187.6317817333334</v>
+        <v>186.2897963333334</v>
       </c>
       <c r="O56">
-        <v>28.14476726000001</v>
+        <v>27.94346945000001</v>
       </c>
       <c r="P56">
-        <v>159.4870144733334</v>
+        <v>158.3463268833334</v>
       </c>
       <c r="Q56">
-        <v>223.1870144733334</v>
+        <v>222.0463268833334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2836780241335113</v>
+        <v>0.2885673076666629</v>
       </c>
       <c r="T56">
-        <v>1.454832383420998</v>
+        <v>1.484734632868655</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.15</v>
       </c>
       <c r="W56">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.211769309779786</v>
+        <v>5.988541828090182</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1557080384499983</v>
+        <v>0.1555414857985814</v>
       </c>
       <c r="C57">
-        <v>1046.998047551376</v>
+        <v>1037.266851174426</v>
       </c>
       <c r="D57">
-        <v>1678.088047551376</v>
+        <v>1680.634851174426</v>
       </c>
       <c r="E57">
-        <v>-61.40999999999985</v>
+        <v>-49.13199999999995</v>
       </c>
       <c r="F57">
-        <v>675.2900000000001</v>
+        <v>687.568</v>
       </c>
       <c r="G57">
         <v>44.2</v>
@@ -5961,28 +5961,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M57">
-        <v>37.343537</v>
+        <v>38.0225104</v>
       </c>
       <c r="N57">
-        <v>186.2897963333334</v>
+        <v>185.6108229333334</v>
       </c>
       <c r="O57">
-        <v>27.94346945000001</v>
+        <v>27.84162344000001</v>
       </c>
       <c r="P57">
-        <v>158.3463268833334</v>
+        <v>157.7691994933334</v>
       </c>
       <c r="Q57">
-        <v>222.0463268833334</v>
+        <v>221.4691994933334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2885673076666629</v>
+        <v>0.2936788313604123</v>
       </c>
       <c r="T57">
-        <v>1.484734632868655</v>
+        <v>1.515996075473023</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.988541828090182</v>
+        <v>5.881603581160001</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1555414857985814</v>
+        <v>0.1553749331471645</v>
       </c>
       <c r="C58">
-        <v>1037.266851174426</v>
+        <v>1027.543397022524</v>
       </c>
       <c r="D58">
-        <v>1680.634851174426</v>
+        <v>1683.189397022524</v>
       </c>
       <c r="E58">
-        <v>-49.13199999999995</v>
+        <v>-36.85399999999993</v>
       </c>
       <c r="F58">
-        <v>687.568</v>
+        <v>699.846</v>
       </c>
       <c r="G58">
         <v>44.2</v>
@@ -6043,28 +6043,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M58">
-        <v>38.0225104</v>
+        <v>38.7014838</v>
       </c>
       <c r="N58">
-        <v>185.6108229333334</v>
+        <v>184.9318495333334</v>
       </c>
       <c r="O58">
-        <v>27.84162344000001</v>
+        <v>27.73977743000001</v>
       </c>
       <c r="P58">
-        <v>157.7691994933334</v>
+        <v>157.1920721033334</v>
       </c>
       <c r="Q58">
-        <v>221.4691994933334</v>
+        <v>220.8920721033334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2936788313604123</v>
+        <v>0.2990281003422431</v>
       </c>
       <c r="T58">
-        <v>1.515996075473023</v>
+        <v>1.548711538663641</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.881603581160001</v>
+        <v>5.778417553420352</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1553749331471645</v>
+        <v>0.1552083804957476</v>
       </c>
       <c r="C59">
-        <v>1027.543397022524</v>
+        <v>1017.827720453696</v>
       </c>
       <c r="D59">
-        <v>1683.189397022524</v>
+        <v>1685.751720453696</v>
       </c>
       <c r="E59">
-        <v>-36.85399999999993</v>
+        <v>-24.57599999999991</v>
       </c>
       <c r="F59">
-        <v>699.846</v>
+        <v>712.124</v>
       </c>
       <c r="G59">
         <v>44.2</v>
@@ -6125,28 +6125,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M59">
-        <v>38.7014838</v>
+        <v>39.3804572</v>
       </c>
       <c r="N59">
-        <v>184.9318495333334</v>
+        <v>184.2528761333334</v>
       </c>
       <c r="O59">
-        <v>27.73977743000001</v>
+        <v>27.63793142000001</v>
       </c>
       <c r="P59">
-        <v>157.1920721033334</v>
+        <v>156.6149447133334</v>
       </c>
       <c r="Q59">
-        <v>220.8920721033334</v>
+        <v>220.3149447133334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2990281003422431</v>
+        <v>0.3046320964184467</v>
       </c>
       <c r="T59">
-        <v>1.548711538663641</v>
+        <v>1.582984881053813</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.778417553420352</v>
+        <v>5.678789664568277</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1552083804957476</v>
+        <v>0.1550418278443307</v>
       </c>
       <c r="C60">
-        <v>1017.827720453697</v>
+        <v>1008.1198570416</v>
       </c>
       <c r="D60">
-        <v>1685.751720453696</v>
+        <v>1688.3218570416</v>
       </c>
       <c r="E60">
-        <v>-24.57600000000002</v>
+        <v>-12.298</v>
       </c>
       <c r="F60">
-        <v>712.1239999999999</v>
+        <v>724.4019999999999</v>
       </c>
       <c r="G60">
         <v>44.2</v>
@@ -6207,28 +6207,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M60">
-        <v>39.3804572</v>
+        <v>40.0594306</v>
       </c>
       <c r="N60">
-        <v>184.2528761333334</v>
+        <v>183.5739027333334</v>
       </c>
       <c r="O60">
-        <v>27.63793142000001</v>
+        <v>27.53608541000001</v>
       </c>
       <c r="P60">
-        <v>156.6149447133334</v>
+        <v>156.0378173233334</v>
       </c>
       <c r="Q60">
-        <v>220.3149447133334</v>
+        <v>219.7378173233334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3046320964184467</v>
+        <v>0.3105094581569042</v>
       </c>
       <c r="T60">
-        <v>1.582984881053813</v>
+        <v>1.61893009380448</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.678789664568278</v>
+        <v>5.582538992287459</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1550418278443307</v>
+        <v>0.1548752751929138</v>
       </c>
       <c r="C61">
-        <v>1008.1198570416</v>
+        <v>998.4198425771677</v>
       </c>
       <c r="D61">
-        <v>1688.3218570416</v>
+        <v>1690.899842577168</v>
       </c>
       <c r="E61">
-        <v>-12.298</v>
+        <v>-0.01999999999998181</v>
       </c>
       <c r="F61">
-        <v>724.4019999999999</v>
+        <v>736.6799999999999</v>
       </c>
       <c r="G61">
         <v>44.2</v>
@@ -6289,28 +6289,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M61">
-        <v>40.0594306</v>
+        <v>40.738404</v>
       </c>
       <c r="N61">
-        <v>183.5739027333334</v>
+        <v>182.8949293333334</v>
       </c>
       <c r="O61">
-        <v>27.53608541000001</v>
+        <v>27.43423940000001</v>
       </c>
       <c r="P61">
-        <v>156.0378173233334</v>
+        <v>155.4606899333334</v>
       </c>
       <c r="Q61">
-        <v>219.7378173233334</v>
+        <v>219.1606899333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3105094581569042</v>
+        <v>0.3166806879822845</v>
       </c>
       <c r="T61">
-        <v>1.61893009380448</v>
+        <v>1.656672567192681</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.582538992287459</v>
+        <v>5.489496675749335</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1548752751929138</v>
+        <v>0.154708722541497</v>
       </c>
       <c r="C62">
-        <v>998.4198425771677</v>
+        <v>988.7277130702704</v>
       </c>
       <c r="D62">
-        <v>1690.899842577168</v>
+        <v>1693.48571307027</v>
       </c>
       <c r="E62">
-        <v>-0.01999999999998181</v>
+        <v>12.25800000000004</v>
       </c>
       <c r="F62">
-        <v>736.6799999999999</v>
+        <v>748.958</v>
       </c>
       <c r="G62">
         <v>44.2</v>
@@ -6371,28 +6371,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M62">
-        <v>40.738404</v>
+        <v>41.4173774</v>
       </c>
       <c r="N62">
-        <v>182.8949293333334</v>
+        <v>182.2159559333334</v>
       </c>
       <c r="O62">
-        <v>27.43423940000001</v>
+        <v>27.33239339000001</v>
       </c>
       <c r="P62">
-        <v>155.4606899333334</v>
+        <v>154.8835625433334</v>
       </c>
       <c r="Q62">
-        <v>219.1606899333334</v>
+        <v>218.5835625433334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3166806879822845</v>
+        <v>0.3231683911320434</v>
       </c>
       <c r="T62">
-        <v>1.656672567192681</v>
+        <v>1.696350552036687</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.489496675749335</v>
+        <v>5.399504926966559</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.154708722541497</v>
+        <v>0.15454216989008</v>
       </c>
       <c r="C63">
-        <v>988.7277130702704</v>
+        <v>979.0435047513967</v>
       </c>
       <c r="D63">
-        <v>1693.48571307027</v>
+        <v>1696.079504751397</v>
       </c>
       <c r="E63">
-        <v>12.25800000000004</v>
+        <v>24.53600000000006</v>
       </c>
       <c r="F63">
-        <v>748.958</v>
+        <v>761.236</v>
       </c>
       <c r="G63">
         <v>44.2</v>
@@ -6453,28 +6453,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M63">
-        <v>41.4173774</v>
+        <v>42.0963508</v>
       </c>
       <c r="N63">
-        <v>182.2159559333334</v>
+        <v>181.5369825333334</v>
       </c>
       <c r="O63">
-        <v>27.33239339000001</v>
+        <v>27.23054738</v>
       </c>
       <c r="P63">
-        <v>154.8835625433334</v>
+        <v>154.3064351533334</v>
       </c>
       <c r="Q63">
-        <v>218.5835625433334</v>
+        <v>218.0064351533334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3231683911320434</v>
+        <v>0.3299975523423159</v>
       </c>
       <c r="T63">
-        <v>1.696350552036687</v>
+        <v>1.738116851872483</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.399504926966559</v>
+        <v>5.312416137821936</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.15454216989008</v>
+        <v>0.1543756172386631</v>
       </c>
       <c r="C64">
-        <v>979.0435047513967</v>
+        <v>969.3672540733395</v>
       </c>
       <c r="D64">
-        <v>1696.079504751397</v>
+        <v>1698.681254073339</v>
       </c>
       <c r="E64">
-        <v>24.53600000000006</v>
+        <v>36.81400000000008</v>
       </c>
       <c r="F64">
-        <v>761.236</v>
+        <v>773.514</v>
       </c>
       <c r="G64">
         <v>44.2</v>
@@ -6535,28 +6535,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M64">
-        <v>42.0963508</v>
+        <v>42.7753242</v>
       </c>
       <c r="N64">
-        <v>181.5369825333334</v>
+        <v>180.8580091333334</v>
       </c>
       <c r="O64">
-        <v>27.23054738</v>
+        <v>27.12870137000001</v>
       </c>
       <c r="P64">
-        <v>154.3064351533334</v>
+        <v>153.7293077633334</v>
       </c>
       <c r="Q64">
-        <v>218.0064351533334</v>
+        <v>217.4293077633334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3299975523423159</v>
+        <v>0.3371958574017923</v>
       </c>
       <c r="T64">
-        <v>1.738116851872483</v>
+        <v>1.782140789537241</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.312416137821936</v>
+        <v>5.228092072142223</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1543756172386631</v>
+        <v>0.1542090645872463</v>
       </c>
       <c r="C65">
-        <v>969.3672540733395</v>
+        <v>959.6989977129075</v>
       </c>
       <c r="D65">
-        <v>1698.681254073339</v>
+        <v>1701.290997712907</v>
       </c>
       <c r="E65">
-        <v>36.81400000000008</v>
+        <v>49.0920000000001</v>
       </c>
       <c r="F65">
-        <v>773.514</v>
+        <v>785.792</v>
       </c>
       <c r="G65">
         <v>44.2</v>
@@ -6617,28 +6617,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M65">
-        <v>42.7753242</v>
+        <v>43.4542976</v>
       </c>
       <c r="N65">
-        <v>180.8580091333334</v>
+        <v>180.1790357333334</v>
       </c>
       <c r="O65">
-        <v>27.12870137000001</v>
+        <v>27.02685536</v>
       </c>
       <c r="P65">
-        <v>153.7293077633334</v>
+        <v>153.1521803733334</v>
       </c>
       <c r="Q65">
-        <v>217.4293077633334</v>
+        <v>216.8521803733333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3371958574017923</v>
+        <v>0.3447940682979063</v>
       </c>
       <c r="T65">
-        <v>1.782140789537241</v>
+        <v>1.828610501516708</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.228092072142223</v>
+        <v>5.146403133515</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1542090645872463</v>
+        <v>0.1540425119358294</v>
       </c>
       <c r="C66">
-        <v>959.6989977129075</v>
+        <v>950.0387725726476</v>
       </c>
       <c r="D66">
-        <v>1701.290997712907</v>
+        <v>1703.908772572648</v>
       </c>
       <c r="E66">
-        <v>49.0920000000001</v>
+        <v>61.37000000000012</v>
       </c>
       <c r="F66">
-        <v>785.792</v>
+        <v>798.0700000000001</v>
       </c>
       <c r="G66">
         <v>44.2</v>
@@ -6699,28 +6699,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M66">
-        <v>43.4542976</v>
+        <v>44.13327100000001</v>
       </c>
       <c r="N66">
-        <v>180.1790357333334</v>
+        <v>179.5000623333334</v>
       </c>
       <c r="O66">
-        <v>27.02685536</v>
+        <v>26.92500935000001</v>
       </c>
       <c r="P66">
-        <v>153.1521803733334</v>
+        <v>152.5750529833334</v>
       </c>
       <c r="Q66">
-        <v>216.8521803733333</v>
+        <v>216.2750529833334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3447940682979063</v>
+        <v>0.3528264626737982</v>
       </c>
       <c r="T66">
-        <v>1.828610501516708</v>
+        <v>1.877735625609287</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.146403133515</v>
+        <v>5.067227700691692</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1540425119358294</v>
+        <v>0.1538759592844125</v>
       </c>
       <c r="C67">
-        <v>950.0387725726476</v>
+        <v>940.3866157825851</v>
       </c>
       <c r="D67">
-        <v>1703.908772572648</v>
+        <v>1706.534615782585</v>
       </c>
       <c r="E67">
-        <v>61.37000000000012</v>
+        <v>73.64800000000002</v>
       </c>
       <c r="F67">
-        <v>798.0700000000001</v>
+        <v>810.348</v>
       </c>
       <c r="G67">
         <v>44.2</v>
@@ -6781,28 +6781,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M67">
-        <v>44.13327100000001</v>
+        <v>44.8122444</v>
       </c>
       <c r="N67">
-        <v>179.5000623333334</v>
+        <v>178.8210889333334</v>
       </c>
       <c r="O67">
-        <v>26.92500935000001</v>
+        <v>26.82316334000001</v>
       </c>
       <c r="P67">
-        <v>152.5750529833334</v>
+        <v>151.9979255933334</v>
       </c>
       <c r="Q67">
-        <v>216.2750529833334</v>
+        <v>215.6979255933334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3528264626737982</v>
+        <v>0.3613313508365074</v>
       </c>
       <c r="T67">
-        <v>1.877735625609287</v>
+        <v>1.929750462883783</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.067227700691692</v>
+        <v>4.990451523408487</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1538759592844125</v>
+        <v>0.1537094066329956</v>
       </c>
       <c r="C68">
-        <v>940.3866157825851</v>
+        <v>930.7425647019782</v>
       </c>
       <c r="D68">
-        <v>1706.534615782585</v>
+        <v>1709.168564701978</v>
       </c>
       <c r="E68">
-        <v>73.64800000000002</v>
+        <v>85.92600000000004</v>
       </c>
       <c r="F68">
-        <v>810.348</v>
+        <v>822.626</v>
       </c>
       <c r="G68">
         <v>44.2</v>
@@ -6863,28 +6863,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M68">
-        <v>44.8122444</v>
+        <v>45.4912178</v>
       </c>
       <c r="N68">
-        <v>178.8210889333334</v>
+        <v>178.1421155333334</v>
       </c>
       <c r="O68">
-        <v>26.82316334000001</v>
+        <v>26.72131733000001</v>
       </c>
       <c r="P68">
-        <v>151.9979255933334</v>
+        <v>151.4207982033334</v>
       </c>
       <c r="Q68">
-        <v>215.6979255933334</v>
+        <v>215.1207982033334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3613313508365074</v>
+        <v>0.3703516867666534</v>
       </c>
       <c r="T68">
-        <v>1.929750462883783</v>
+        <v>1.984917714538551</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.990451523408487</v>
+        <v>4.915967172312836</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1537094066329956</v>
+        <v>0.1535428539815787</v>
       </c>
       <c r="C69">
-        <v>930.7425647019782</v>
+        <v>921.1066569210889</v>
       </c>
       <c r="D69">
-        <v>1709.168564701978</v>
+        <v>1711.810656921089</v>
       </c>
       <c r="E69">
-        <v>85.92600000000004</v>
+        <v>98.20400000000006</v>
       </c>
       <c r="F69">
-        <v>822.626</v>
+        <v>834.904</v>
       </c>
       <c r="G69">
         <v>44.2</v>
@@ -6945,28 +6945,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M69">
-        <v>45.4912178</v>
+        <v>46.1701912</v>
       </c>
       <c r="N69">
-        <v>178.1421155333334</v>
+        <v>177.4631421333334</v>
       </c>
       <c r="O69">
-        <v>26.72131733000001</v>
+        <v>26.61947132000001</v>
       </c>
       <c r="P69">
-        <v>151.4207982033334</v>
+        <v>150.8436708133334</v>
       </c>
       <c r="Q69">
-        <v>215.1207982033334</v>
+        <v>214.5436708133334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3703516867666534</v>
+        <v>0.3799357936924335</v>
       </c>
       <c r="T69">
-        <v>1.984917714538551</v>
+        <v>2.043532919421742</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.915967172312836</v>
+        <v>4.843673537425883</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1535428539815787</v>
+        <v>0.1533763013301618</v>
       </c>
       <c r="C70">
-        <v>921.1066569210889</v>
+        <v>911.4789302629733</v>
       </c>
       <c r="D70">
-        <v>1711.810656921089</v>
+        <v>1714.460930262973</v>
       </c>
       <c r="E70">
-        <v>98.20400000000006</v>
+        <v>110.4820000000001</v>
       </c>
       <c r="F70">
-        <v>834.904</v>
+        <v>847.182</v>
       </c>
       <c r="G70">
         <v>44.2</v>
@@ -7027,28 +7027,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M70">
-        <v>46.1701912</v>
+        <v>46.8491646</v>
       </c>
       <c r="N70">
-        <v>177.4631421333334</v>
+        <v>176.7841687333334</v>
       </c>
       <c r="O70">
-        <v>26.61947132000001</v>
+        <v>26.51762531000001</v>
       </c>
       <c r="P70">
-        <v>150.8436708133334</v>
+        <v>150.2665434233334</v>
       </c>
       <c r="Q70">
-        <v>214.5436708133334</v>
+        <v>213.9665434233334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3799357936924335</v>
+        <v>0.3901382300972963</v>
       </c>
       <c r="T70">
-        <v>2.043532919421742</v>
+        <v>2.105929750426429</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.843673537425883</v>
+        <v>4.773475370216812</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1533763013301618</v>
+        <v>0.1532097486787449</v>
       </c>
       <c r="C71">
-        <v>911.4789302629733</v>
+        <v>901.8594227852866</v>
       </c>
       <c r="D71">
-        <v>1714.460930262973</v>
+        <v>1717.119422785287</v>
       </c>
       <c r="E71">
-        <v>110.4820000000001</v>
+        <v>122.7600000000001</v>
       </c>
       <c r="F71">
-        <v>847.182</v>
+        <v>859.46</v>
       </c>
       <c r="G71">
         <v>44.2</v>
@@ -7109,28 +7109,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M71">
-        <v>46.8491646</v>
+        <v>47.52813800000001</v>
       </c>
       <c r="N71">
-        <v>176.7841687333334</v>
+        <v>176.1051953333334</v>
       </c>
       <c r="O71">
-        <v>26.51762531000001</v>
+        <v>26.4157793</v>
       </c>
       <c r="P71">
-        <v>150.2665434233334</v>
+        <v>149.6894160333334</v>
       </c>
       <c r="Q71">
-        <v>213.9665434233334</v>
+        <v>213.3894160333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3901382300972963</v>
+        <v>0.4010208289291498</v>
       </c>
       <c r="T71">
-        <v>2.105929750426429</v>
+        <v>2.172486370164762</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.773475370216812</v>
+        <v>4.705282864928</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1532097486787449</v>
+        <v>0.153043196027328</v>
       </c>
       <c r="C72">
-        <v>901.8594227852866</v>
+        <v>892.2481727821018</v>
       </c>
       <c r="D72">
-        <v>1717.119422785287</v>
+        <v>1719.786172782102</v>
       </c>
       <c r="E72">
-        <v>122.7600000000001</v>
+        <v>135.0380000000001</v>
       </c>
       <c r="F72">
-        <v>859.46</v>
+        <v>871.7380000000001</v>
       </c>
       <c r="G72">
         <v>44.2</v>
@@ -7191,28 +7191,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M72">
-        <v>47.52813800000001</v>
+        <v>48.2071114</v>
       </c>
       <c r="N72">
-        <v>176.1051953333334</v>
+        <v>175.4262219333334</v>
       </c>
       <c r="O72">
-        <v>26.4157793</v>
+        <v>26.31393329</v>
       </c>
       <c r="P72">
-        <v>149.6894160333334</v>
+        <v>149.1122886433334</v>
       </c>
       <c r="Q72">
-        <v>213.3894160333334</v>
+        <v>212.8122886433334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4010208289291498</v>
+        <v>0.4126539518183727</v>
       </c>
       <c r="T72">
-        <v>2.172486370164762</v>
+        <v>2.243633101609187</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.705282864928</v>
+        <v>4.639011275281128</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.153043196027328</v>
+        <v>0.1528766433759111</v>
       </c>
       <c r="C73">
-        <v>892.248172782102</v>
+        <v>882.6452187857518</v>
       </c>
       <c r="D73">
-        <v>1719.786172782102</v>
+        <v>1722.461218785752</v>
       </c>
       <c r="E73">
-        <v>135.038</v>
+        <v>147.316</v>
       </c>
       <c r="F73">
-        <v>871.7379999999999</v>
+        <v>884.016</v>
       </c>
       <c r="G73">
         <v>44.2</v>
@@ -7273,28 +7273,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M73">
-        <v>48.2071114</v>
+        <v>48.8860848</v>
       </c>
       <c r="N73">
-        <v>175.4262219333334</v>
+        <v>174.7472485333334</v>
       </c>
       <c r="O73">
-        <v>26.31393329</v>
+        <v>26.21208728000001</v>
       </c>
       <c r="P73">
-        <v>149.1122886433334</v>
+        <v>148.5351612533334</v>
       </c>
       <c r="Q73">
-        <v>212.8122886433334</v>
+        <v>212.2351612533334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4126539518183726</v>
+        <v>0.4251180120568255</v>
       </c>
       <c r="T73">
-        <v>2.243633101609186</v>
+        <v>2.319861742442499</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.639011275281128</v>
+        <v>4.574580563124446</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1528766433759111</v>
+        <v>0.1527100907244943</v>
       </c>
       <c r="C74">
-        <v>882.6452187857518</v>
+        <v>873.0505995686827</v>
       </c>
       <c r="D74">
-        <v>1722.461218785752</v>
+        <v>1725.144599568683</v>
       </c>
       <c r="E74">
-        <v>147.316</v>
+        <v>159.5940000000001</v>
       </c>
       <c r="F74">
-        <v>884.016</v>
+        <v>896.294</v>
       </c>
       <c r="G74">
         <v>44.2</v>
@@ -7355,28 +7355,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M74">
-        <v>48.8860848</v>
+        <v>49.5650582</v>
       </c>
       <c r="N74">
-        <v>174.7472485333334</v>
+        <v>174.0682751333334</v>
       </c>
       <c r="O74">
-        <v>26.21208728000001</v>
+        <v>26.11024127000001</v>
       </c>
       <c r="P74">
-        <v>148.5351612533334</v>
+        <v>147.9580338633334</v>
       </c>
       <c r="Q74">
-        <v>212.2351612533334</v>
+        <v>211.6580338633333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4251180120568255</v>
+        <v>0.4385053360166453</v>
       </c>
       <c r="T74">
-        <v>2.319861742442499</v>
+        <v>2.401736949263463</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.574580563124446</v>
+        <v>4.511915075958356</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1527100907244943</v>
+        <v>0.1541160380730774</v>
       </c>
       <c r="C75">
-        <v>873.0505995686827</v>
+        <v>838.3801402539351</v>
       </c>
       <c r="D75">
-        <v>1725.144599568683</v>
+        <v>1702.752140253935</v>
       </c>
       <c r="E75">
-        <v>159.5940000000001</v>
+        <v>171.8720000000001</v>
       </c>
       <c r="F75">
-        <v>896.294</v>
+        <v>908.572</v>
       </c>
       <c r="G75">
         <v>44.2</v>
@@ -7437,45 +7437,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M75">
-        <v>49.5650582</v>
+        <v>52.5154616</v>
       </c>
       <c r="N75">
-        <v>174.0682751333334</v>
+        <v>171.1178717333334</v>
       </c>
       <c r="O75">
-        <v>26.11024127000001</v>
+        <v>25.66768076000001</v>
       </c>
       <c r="P75">
-        <v>147.9580338633334</v>
+        <v>145.4501909733334</v>
       </c>
       <c r="Q75">
-        <v>211.6580338633333</v>
+        <v>209.1501909733334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4385053360166453</v>
+        <v>0.4529224541272206</v>
       </c>
       <c r="T75">
-        <v>2.401736949263463</v>
+        <v>2.489910248916811</v>
       </c>
       <c r="U75">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V75">
         <v>0.15</v>
       </c>
       <c r="W75">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.511915075958356</v>
+        <v>4.258428404128002</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1541160380730774</v>
+        <v>0.1539707354216605</v>
       </c>
       <c r="C76">
-        <v>838.3801402539351</v>
+        <v>828.3893984455365</v>
       </c>
       <c r="D76">
-        <v>1702.752140253935</v>
+        <v>1705.039398445536</v>
       </c>
       <c r="E76">
-        <v>171.8720000000001</v>
+        <v>184.15</v>
       </c>
       <c r="F76">
-        <v>908.572</v>
+        <v>920.8499999999999</v>
       </c>
       <c r="G76">
         <v>44.2</v>
@@ -7519,28 +7519,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M76">
-        <v>52.5154616</v>
+        <v>53.22513</v>
       </c>
       <c r="N76">
-        <v>171.1178717333334</v>
+        <v>170.4082033333334</v>
       </c>
       <c r="O76">
-        <v>25.66768076000001</v>
+        <v>25.5612305</v>
       </c>
       <c r="P76">
-        <v>145.4501909733334</v>
+        <v>144.8469728333334</v>
       </c>
       <c r="Q76">
-        <v>209.1501909733334</v>
+        <v>208.5469728333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4529224541272206</v>
+        <v>0.4684929416866419</v>
       </c>
       <c r="T76">
-        <v>2.489910248916811</v>
+        <v>2.585137412542426</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.258428404128002</v>
+        <v>4.201649358739629</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1539707354216605</v>
+        <v>0.1538254327702436</v>
       </c>
       <c r="C77">
-        <v>828.3893984455365</v>
+        <v>818.4048097192622</v>
       </c>
       <c r="D77">
-        <v>1705.039398445536</v>
+        <v>1707.332809719262</v>
       </c>
       <c r="E77">
-        <v>184.15</v>
+        <v>196.428</v>
       </c>
       <c r="F77">
-        <v>920.8499999999999</v>
+        <v>933.1279999999999</v>
       </c>
       <c r="G77">
         <v>44.2</v>
@@ -7601,28 +7601,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M77">
-        <v>53.22513</v>
+        <v>53.9347984</v>
       </c>
       <c r="N77">
-        <v>170.4082033333334</v>
+        <v>169.6985349333334</v>
       </c>
       <c r="O77">
-        <v>25.5612305</v>
+        <v>25.45478024000001</v>
       </c>
       <c r="P77">
-        <v>144.8469728333334</v>
+        <v>144.2437546933334</v>
       </c>
       <c r="Q77">
-        <v>208.5469728333334</v>
+        <v>207.9437546933333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4684929416866419</v>
+        <v>0.4853609698760149</v>
       </c>
       <c r="T77">
-        <v>2.585137412542426</v>
+        <v>2.688300173136842</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.201649358739629</v>
+        <v>4.146364498756212</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1538254327702436</v>
+        <v>0.1536801301188267</v>
       </c>
       <c r="C78">
-        <v>818.4048097192622</v>
+        <v>808.4263989376846</v>
       </c>
       <c r="D78">
-        <v>1707.332809719262</v>
+        <v>1709.632398937684</v>
       </c>
       <c r="E78">
-        <v>196.428</v>
+        <v>208.706</v>
       </c>
       <c r="F78">
-        <v>933.1279999999999</v>
+        <v>945.4059999999999</v>
       </c>
       <c r="G78">
         <v>44.2</v>
@@ -7683,28 +7683,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M78">
-        <v>53.9347984</v>
+        <v>54.6444668</v>
       </c>
       <c r="N78">
-        <v>169.6985349333334</v>
+        <v>168.9888665333334</v>
       </c>
       <c r="O78">
-        <v>25.45478024000001</v>
+        <v>25.34832998000001</v>
       </c>
       <c r="P78">
-        <v>144.2437546933334</v>
+        <v>143.6405365533334</v>
       </c>
       <c r="Q78">
-        <v>207.9437546933333</v>
+        <v>207.3405365533334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4853609698760149</v>
+        <v>0.5036957831253334</v>
       </c>
       <c r="T78">
-        <v>2.688300173136842</v>
+        <v>2.800433608565555</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.146364498756212</v>
+        <v>4.092515609161977</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1536801301188267</v>
+        <v>0.1535348274674098</v>
       </c>
       <c r="C79">
-        <v>808.4263989376846</v>
+        <v>798.4541910975038</v>
       </c>
       <c r="D79">
-        <v>1709.632398937684</v>
+        <v>1711.938191097504</v>
       </c>
       <c r="E79">
-        <v>208.706</v>
+        <v>220.984</v>
       </c>
       <c r="F79">
-        <v>945.4059999999999</v>
+        <v>957.684</v>
       </c>
       <c r="G79">
         <v>44.2</v>
@@ -7765,28 +7765,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M79">
-        <v>54.6444668</v>
+        <v>55.3541352</v>
       </c>
       <c r="N79">
-        <v>168.9888665333334</v>
+        <v>168.2791981333334</v>
       </c>
       <c r="O79">
-        <v>25.34832998000001</v>
+        <v>25.24187972000001</v>
       </c>
       <c r="P79">
-        <v>143.6405365533334</v>
+        <v>143.0373184133334</v>
       </c>
       <c r="Q79">
-        <v>207.3405365533334</v>
+        <v>206.7373184133334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5036957831253334</v>
+        <v>0.5236973975791355</v>
       </c>
       <c r="T79">
-        <v>2.800433608565555</v>
+        <v>2.922760992669605</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.092515609161977</v>
+        <v>4.040047460326566</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1535348274674098</v>
+        <v>0.1557397748159929</v>
       </c>
       <c r="C80">
-        <v>798.4541910975038</v>
+        <v>751.8416330932114</v>
       </c>
       <c r="D80">
-        <v>1711.938191097504</v>
+        <v>1677.603633093211</v>
       </c>
       <c r="E80">
-        <v>220.984</v>
+        <v>233.2620000000001</v>
       </c>
       <c r="F80">
-        <v>957.684</v>
+        <v>969.962</v>
       </c>
       <c r="G80">
         <v>44.2</v>
@@ -7847,45 +7847,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M80">
-        <v>55.3541352</v>
+        <v>59.4586706</v>
       </c>
       <c r="N80">
-        <v>168.2791981333334</v>
+        <v>164.1746627333334</v>
       </c>
       <c r="O80">
-        <v>25.24187972000001</v>
+        <v>24.62619941000001</v>
       </c>
       <c r="P80">
-        <v>143.0373184133334</v>
+        <v>139.5484633233334</v>
       </c>
       <c r="Q80">
-        <v>206.7373184133334</v>
+        <v>203.2484633233334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5236973975791355</v>
+        <v>0.5456039276952043</v>
       </c>
       <c r="T80">
-        <v>2.922760992669605</v>
+        <v>3.056738603831185</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.15</v>
       </c>
       <c r="W80">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.040047460326566</v>
+        <v>3.761155960546037</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1557397748159929</v>
+        <v>0.155624222164576</v>
       </c>
       <c r="C81">
-        <v>751.8416330932114</v>
+        <v>741.3287404985706</v>
       </c>
       <c r="D81">
-        <v>1677.603633093211</v>
+        <v>1679.368740498571</v>
       </c>
       <c r="E81">
-        <v>233.2620000000001</v>
+        <v>245.5400000000001</v>
       </c>
       <c r="F81">
-        <v>969.962</v>
+        <v>982.24</v>
       </c>
       <c r="G81">
         <v>44.2</v>
@@ -7929,28 +7929,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M81">
-        <v>59.4586706</v>
+        <v>60.211312</v>
       </c>
       <c r="N81">
-        <v>164.1746627333334</v>
+        <v>163.4220213333334</v>
       </c>
       <c r="O81">
-        <v>24.62619941000001</v>
+        <v>24.51330320000001</v>
       </c>
       <c r="P81">
-        <v>139.5484633233334</v>
+        <v>138.9087181333334</v>
       </c>
       <c r="Q81">
-        <v>203.2484633233334</v>
+        <v>202.6087181333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5456039276952043</v>
+        <v>0.5697011108228801</v>
       </c>
       <c r="T81">
-        <v>3.056738603831185</v>
+        <v>3.204113976108922</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.761155960546037</v>
+        <v>3.714141511039211</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.155624222164576</v>
+        <v>0.1555086695131591</v>
       </c>
       <c r="C82">
-        <v>741.3287404985706</v>
+        <v>730.8195661668826</v>
       </c>
       <c r="D82">
-        <v>1679.368740498571</v>
+        <v>1681.137566166883</v>
       </c>
       <c r="E82">
-        <v>245.5400000000001</v>
+        <v>257.8180000000001</v>
       </c>
       <c r="F82">
-        <v>982.24</v>
+        <v>994.518</v>
       </c>
       <c r="G82">
         <v>44.2</v>
@@ -8011,28 +8011,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M82">
-        <v>60.211312</v>
+        <v>60.9639534</v>
       </c>
       <c r="N82">
-        <v>163.4220213333334</v>
+        <v>162.6693799333334</v>
       </c>
       <c r="O82">
-        <v>24.51330320000001</v>
+        <v>24.40040699</v>
       </c>
       <c r="P82">
-        <v>138.9087181333334</v>
+        <v>138.2689729433334</v>
       </c>
       <c r="Q82">
-        <v>202.6087181333334</v>
+        <v>201.9689729433334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5697011108228801</v>
+        <v>0.5963348395429429</v>
       </c>
       <c r="T82">
-        <v>3.204113976108922</v>
+        <v>3.367002545468527</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.714141511039211</v>
+        <v>3.668287912137492</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1555086695131591</v>
+        <v>0.1553931168617422</v>
       </c>
       <c r="C83">
-        <v>730.8195661668826</v>
+        <v>720.3141218595197</v>
       </c>
       <c r="D83">
-        <v>1681.137566166883</v>
+        <v>1682.91012185952</v>
       </c>
       <c r="E83">
-        <v>257.8180000000001</v>
+        <v>270.0960000000001</v>
       </c>
       <c r="F83">
-        <v>994.518</v>
+        <v>1006.796</v>
       </c>
       <c r="G83">
         <v>44.2</v>
@@ -8093,28 +8093,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M83">
-        <v>60.9639534</v>
+        <v>61.7165948</v>
       </c>
       <c r="N83">
-        <v>162.6693799333334</v>
+        <v>161.9167385333334</v>
       </c>
       <c r="O83">
-        <v>24.40040699</v>
+        <v>24.28751078000001</v>
       </c>
       <c r="P83">
-        <v>138.2689729433334</v>
+        <v>137.6292277533334</v>
       </c>
       <c r="Q83">
-        <v>201.9689729433334</v>
+        <v>201.3292277533334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5963348395429429</v>
+        <v>0.6259278714541237</v>
       </c>
       <c r="T83">
-        <v>3.367002545468527</v>
+        <v>3.547989844756976</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.668287912137492</v>
+        <v>3.623552693696791</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1553931168617422</v>
+        <v>0.1552775642103253</v>
       </c>
       <c r="C84">
-        <v>720.3141218595197</v>
+        <v>709.8124193875103</v>
       </c>
       <c r="D84">
-        <v>1682.91012185952</v>
+        <v>1684.68641938751</v>
       </c>
       <c r="E84">
-        <v>270.0960000000001</v>
+        <v>282.3740000000001</v>
       </c>
       <c r="F84">
-        <v>1006.796</v>
+        <v>1019.074</v>
       </c>
       <c r="G84">
         <v>44.2</v>
@@ -8175,28 +8175,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M84">
-        <v>61.7165948</v>
+        <v>62.4692362</v>
       </c>
       <c r="N84">
-        <v>161.9167385333334</v>
+        <v>161.1640971333334</v>
       </c>
       <c r="O84">
-        <v>24.28751078000001</v>
+        <v>24.17461457000001</v>
       </c>
       <c r="P84">
-        <v>137.6292277533334</v>
+        <v>136.9894825633334</v>
       </c>
       <c r="Q84">
-        <v>201.3292277533334</v>
+        <v>200.6894825633333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6259278714541237</v>
+        <v>0.6590024365313257</v>
       </c>
       <c r="T84">
-        <v>3.547989844756976</v>
+        <v>3.750269767491126</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.623552693696791</v>
+        <v>3.57989543232695</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1552775642103253</v>
+        <v>0.1551620115589085</v>
       </c>
       <c r="C85">
-        <v>709.8124193875103</v>
+        <v>699.3144706117996</v>
       </c>
       <c r="D85">
-        <v>1684.68641938751</v>
+        <v>1686.4664706118</v>
       </c>
       <c r="E85">
-        <v>282.3740000000001</v>
+        <v>294.6520000000002</v>
       </c>
       <c r="F85">
-        <v>1019.074</v>
+        <v>1031.352</v>
       </c>
       <c r="G85">
         <v>44.2</v>
@@ -8257,28 +8257,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M85">
-        <v>62.4692362</v>
+        <v>63.22187760000001</v>
       </c>
       <c r="N85">
-        <v>161.1640971333334</v>
+        <v>160.4114557333334</v>
       </c>
       <c r="O85">
-        <v>24.17461457000001</v>
+        <v>24.06171836000001</v>
       </c>
       <c r="P85">
-        <v>136.9894825633334</v>
+        <v>136.3497373733334</v>
       </c>
       <c r="Q85">
-        <v>200.6894825633333</v>
+        <v>200.0497373733334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6590024365313257</v>
+        <v>0.6962113222431782</v>
       </c>
       <c r="T85">
-        <v>3.750269767491126</v>
+        <v>3.977834680567045</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.57989543232695</v>
+        <v>3.537277629561153</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1551620115589085</v>
+        <v>0.1570694589074916</v>
       </c>
       <c r="C86">
-        <v>699.3144706117998</v>
+        <v>658.1260577327614</v>
       </c>
       <c r="D86">
-        <v>1686.4664706118</v>
+        <v>1657.556057732761</v>
       </c>
       <c r="E86">
-        <v>294.6519999999999</v>
+        <v>306.9299999999999</v>
       </c>
       <c r="F86">
-        <v>1031.352</v>
+        <v>1043.63</v>
       </c>
       <c r="G86">
         <v>44.2</v>
@@ -8339,45 +8339,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M86">
-        <v>63.22187759999999</v>
+        <v>66.896683</v>
       </c>
       <c r="N86">
-        <v>160.4114557333334</v>
+        <v>156.7366503333334</v>
       </c>
       <c r="O86">
-        <v>24.06171836000001</v>
+        <v>23.51049755000001</v>
       </c>
       <c r="P86">
-        <v>136.3497373733334</v>
+        <v>133.2261527833334</v>
       </c>
       <c r="Q86">
-        <v>200.0497373733334</v>
+        <v>196.9261527833334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6962113222431777</v>
+        <v>0.7383813927166103</v>
       </c>
       <c r="T86">
-        <v>3.977834680567042</v>
+        <v>4.235741582053082</v>
       </c>
       <c r="U86">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V86">
         <v>0.15</v>
       </c>
       <c r="W86">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.537277629561154</v>
+        <v>3.342965948451187</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1570694589074916</v>
+        <v>0.1569777062560747</v>
       </c>
       <c r="C87">
-        <v>658.1260577327614</v>
+        <v>647.2160043138758</v>
       </c>
       <c r="D87">
-        <v>1657.556057732761</v>
+        <v>1658.924004313876</v>
       </c>
       <c r="E87">
-        <v>306.9299999999999</v>
+        <v>319.208</v>
       </c>
       <c r="F87">
-        <v>1043.63</v>
+        <v>1055.908</v>
       </c>
       <c r="G87">
         <v>44.2</v>
@@ -8421,28 +8421,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M87">
-        <v>66.896683</v>
+        <v>67.68370279999999</v>
       </c>
       <c r="N87">
-        <v>156.7366503333334</v>
+        <v>155.9496305333334</v>
       </c>
       <c r="O87">
-        <v>23.51049755000001</v>
+        <v>23.39244458000001</v>
       </c>
       <c r="P87">
-        <v>133.2261527833334</v>
+        <v>132.5571859533334</v>
       </c>
       <c r="Q87">
-        <v>196.9261527833334</v>
+        <v>196.2571859533334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7383813927166103</v>
+        <v>0.7865757589719617</v>
       </c>
       <c r="T87">
-        <v>4.235741582053082</v>
+        <v>4.530492326608556</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.342965948451187</v>
+        <v>3.304094251376173</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1569777062560747</v>
+        <v>0.1568859536046578</v>
       </c>
       <c r="C88">
-        <v>647.2160043138758</v>
+        <v>636.3082106356994</v>
       </c>
       <c r="D88">
-        <v>1658.924004313876</v>
+        <v>1660.294210635699</v>
       </c>
       <c r="E88">
-        <v>319.208</v>
+        <v>331.486</v>
       </c>
       <c r="F88">
-        <v>1055.908</v>
+        <v>1068.186</v>
       </c>
       <c r="G88">
         <v>44.2</v>
@@ -8503,28 +8503,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M88">
-        <v>67.68370279999999</v>
+        <v>68.4707226</v>
       </c>
       <c r="N88">
-        <v>155.9496305333334</v>
+        <v>155.1626107333334</v>
       </c>
       <c r="O88">
-        <v>23.39244458000001</v>
+        <v>23.27439161000001</v>
       </c>
       <c r="P88">
-        <v>132.5571859533334</v>
+        <v>131.8882191233334</v>
       </c>
       <c r="Q88">
-        <v>196.2571859533334</v>
+        <v>195.5882191233334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7865757589719617</v>
+        <v>0.842184643112752</v>
       </c>
       <c r="T88">
-        <v>4.530492326608556</v>
+        <v>4.87058933955718</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.304094251376173</v>
+        <v>3.266116156532769</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1568859536046578</v>
+        <v>0.1567942009532409</v>
       </c>
       <c r="C89">
-        <v>636.3082106356994</v>
+        <v>625.4026823022339</v>
       </c>
       <c r="D89">
-        <v>1660.294210635699</v>
+        <v>1661.666682302234</v>
       </c>
       <c r="E89">
-        <v>331.486</v>
+        <v>343.764</v>
       </c>
       <c r="F89">
-        <v>1068.186</v>
+        <v>1080.464</v>
       </c>
       <c r="G89">
         <v>44.2</v>
@@ -8585,28 +8585,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M89">
-        <v>68.4707226</v>
+        <v>69.2577424</v>
       </c>
       <c r="N89">
-        <v>155.1626107333334</v>
+        <v>154.3755909333334</v>
       </c>
       <c r="O89">
-        <v>23.27439161000001</v>
+        <v>23.15633864000001</v>
       </c>
       <c r="P89">
-        <v>131.8882191233334</v>
+        <v>131.2192522933334</v>
       </c>
       <c r="Q89">
-        <v>195.5882191233334</v>
+        <v>194.9192522933334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.842184643112752</v>
+        <v>0.9070616746103407</v>
       </c>
       <c r="T89">
-        <v>4.87058933955718</v>
+        <v>5.267369187997243</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.266116156532769</v>
+        <v>3.229001200208533</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1567942009532409</v>
+        <v>0.156702448301824</v>
       </c>
       <c r="C90">
-        <v>625.4026823022339</v>
+        <v>614.499424936025</v>
       </c>
       <c r="D90">
-        <v>1661.666682302234</v>
+        <v>1663.041424936025</v>
       </c>
       <c r="E90">
-        <v>343.764</v>
+        <v>356.042</v>
       </c>
       <c r="F90">
-        <v>1080.464</v>
+        <v>1092.742</v>
       </c>
       <c r="G90">
         <v>44.2</v>
@@ -8667,28 +8667,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M90">
-        <v>69.2577424</v>
+        <v>70.04476220000001</v>
       </c>
       <c r="N90">
-        <v>154.3755909333334</v>
+        <v>153.5885711333334</v>
       </c>
       <c r="O90">
-        <v>23.15633864000001</v>
+        <v>23.03828567</v>
       </c>
       <c r="P90">
-        <v>131.2192522933334</v>
+        <v>130.5502854633334</v>
       </c>
       <c r="Q90">
-        <v>194.9192522933334</v>
+        <v>194.2502854633334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9070616746103407</v>
+        <v>0.9837345300165817</v>
       </c>
       <c r="T90">
-        <v>5.267369187997243</v>
+        <v>5.736290827062771</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.229001200208533</v>
+        <v>3.192720287846639</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.156702448301824</v>
+        <v>0.1566106956504071</v>
       </c>
       <c r="C91">
-        <v>614.499424936025</v>
+        <v>603.5984441782414</v>
       </c>
       <c r="D91">
-        <v>1663.041424936025</v>
+        <v>1664.418444178241</v>
       </c>
       <c r="E91">
-        <v>356.042</v>
+        <v>368.3200000000001</v>
       </c>
       <c r="F91">
-        <v>1092.742</v>
+        <v>1105.02</v>
       </c>
       <c r="G91">
         <v>44.2</v>
@@ -8749,28 +8749,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M91">
-        <v>70.04476220000001</v>
+        <v>70.831782</v>
       </c>
       <c r="N91">
-        <v>153.5885711333334</v>
+        <v>152.8015513333334</v>
       </c>
       <c r="O91">
-        <v>23.03828567</v>
+        <v>22.92023270000001</v>
       </c>
       <c r="P91">
-        <v>130.5502854633334</v>
+        <v>129.8813186333334</v>
       </c>
       <c r="Q91">
-        <v>194.2502854633334</v>
+        <v>193.5813186333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9837345300165817</v>
+        <v>1.075741956504071</v>
       </c>
       <c r="T91">
-        <v>5.736290827062771</v>
+        <v>6.298996793941405</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.192720287846639</v>
+        <v>3.157245617981676</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1566106956504071</v>
+        <v>0.1565189429989902</v>
       </c>
       <c r="C92">
-        <v>603.5984441782414</v>
+        <v>592.6997456887509</v>
       </c>
       <c r="D92">
-        <v>1664.418444178241</v>
+        <v>1665.797745688751</v>
       </c>
       <c r="E92">
-        <v>368.3200000000001</v>
+        <v>380.5980000000001</v>
       </c>
       <c r="F92">
-        <v>1105.02</v>
+        <v>1117.298</v>
       </c>
       <c r="G92">
         <v>44.2</v>
@@ -8831,28 +8831,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M92">
-        <v>70.831782</v>
+        <v>71.6188018</v>
       </c>
       <c r="N92">
-        <v>152.8015513333334</v>
+        <v>152.0145315333334</v>
       </c>
       <c r="O92">
-        <v>22.92023270000001</v>
+        <v>22.80217973000001</v>
       </c>
       <c r="P92">
-        <v>129.8813186333334</v>
+        <v>129.2123518033334</v>
       </c>
       <c r="Q92">
-        <v>193.5813186333334</v>
+        <v>192.9123518033334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.075741956504071</v>
+        <v>1.188195477766558</v>
       </c>
       <c r="T92">
-        <v>6.298996793941405</v>
+        <v>6.986748531237512</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.157245617981676</v>
+        <v>3.122550611190669</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1565189429989902</v>
+        <v>0.1564271903475733</v>
       </c>
       <c r="C93">
-        <v>592.6997456887509</v>
+        <v>581.8033351461979</v>
       </c>
       <c r="D93">
-        <v>1665.797745688751</v>
+        <v>1667.179335146198</v>
       </c>
       <c r="E93">
-        <v>380.5980000000001</v>
+        <v>392.8760000000001</v>
       </c>
       <c r="F93">
-        <v>1117.298</v>
+        <v>1129.576</v>
       </c>
       <c r="G93">
         <v>44.2</v>
@@ -8913,28 +8913,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M93">
-        <v>71.6188018</v>
+        <v>72.40582160000001</v>
       </c>
       <c r="N93">
-        <v>152.0145315333334</v>
+        <v>151.2275117333334</v>
       </c>
       <c r="O93">
-        <v>22.80217973000001</v>
+        <v>22.68412676</v>
       </c>
       <c r="P93">
-        <v>129.2123518033334</v>
+        <v>128.5433849733334</v>
       </c>
       <c r="Q93">
-        <v>192.9123518033334</v>
+        <v>192.2433849733334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.188195477766558</v>
+        <v>1.328762379344667</v>
       </c>
       <c r="T93">
-        <v>6.986748531237512</v>
+        <v>7.846438202857648</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.122550611190669</v>
+        <v>3.088609843677726</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1564271903475733</v>
+        <v>0.1563354376961564</v>
       </c>
       <c r="C94">
-        <v>581.8033351461979</v>
+        <v>570.9092182480827</v>
       </c>
       <c r="D94">
-        <v>1667.179335146198</v>
+        <v>1668.563218248083</v>
       </c>
       <c r="E94">
-        <v>392.8760000000001</v>
+        <v>405.1540000000001</v>
       </c>
       <c r="F94">
-        <v>1129.576</v>
+        <v>1141.854</v>
       </c>
       <c r="G94">
         <v>44.2</v>
@@ -8995,28 +8995,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M94">
-        <v>72.40582160000001</v>
+        <v>73.19284140000001</v>
       </c>
       <c r="N94">
-        <v>151.2275117333334</v>
+        <v>150.4404919333334</v>
       </c>
       <c r="O94">
-        <v>22.68412676</v>
+        <v>22.56607379</v>
       </c>
       <c r="P94">
-        <v>128.5433849733334</v>
+        <v>127.8744181433334</v>
       </c>
       <c r="Q94">
-        <v>192.2433849733334</v>
+        <v>191.5744181433334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.328762379344667</v>
+        <v>1.509491252802236</v>
       </c>
       <c r="T94">
-        <v>7.846438202857648</v>
+        <v>8.951753494940679</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.088609843677726</v>
+        <v>3.055398985143557</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1563354376961564</v>
+        <v>0.1562436850447395</v>
       </c>
       <c r="C95">
-        <v>570.9092182480827</v>
+        <v>560.0174007108369</v>
       </c>
       <c r="D95">
-        <v>1668.563218248083</v>
+        <v>1669.949400710837</v>
       </c>
       <c r="E95">
-        <v>405.1540000000001</v>
+        <v>417.4320000000001</v>
       </c>
       <c r="F95">
-        <v>1141.854</v>
+        <v>1154.132</v>
       </c>
       <c r="G95">
         <v>44.2</v>
@@ -9077,28 +9077,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M95">
-        <v>73.19284140000001</v>
+        <v>73.9798612</v>
       </c>
       <c r="N95">
-        <v>150.4404919333334</v>
+        <v>149.6534721333334</v>
       </c>
       <c r="O95">
-        <v>22.56607379</v>
+        <v>22.44802082</v>
       </c>
       <c r="P95">
-        <v>127.8744181433334</v>
+        <v>127.2054513133334</v>
       </c>
       <c r="Q95">
-        <v>191.5744181433334</v>
+        <v>190.9054513133333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.509491252802236</v>
+        <v>1.750463084078994</v>
       </c>
       <c r="T95">
-        <v>8.951753494940679</v>
+        <v>10.42550721771805</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.055398985143557</v>
+        <v>3.022894740620754</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1562436850447395</v>
+        <v>0.1624504323933227</v>
       </c>
       <c r="C96">
-        <v>560.0174007108369</v>
+        <v>458.8845734935546</v>
       </c>
       <c r="D96">
-        <v>1669.949400710837</v>
+        <v>1581.094573493555</v>
       </c>
       <c r="E96">
-        <v>417.4320000000001</v>
+        <v>429.7100000000002</v>
       </c>
       <c r="F96">
-        <v>1154.132</v>
+        <v>1166.41</v>
       </c>
       <c r="G96">
         <v>44.2</v>
@@ -9159,45 +9159,45 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M96">
-        <v>73.9798612</v>
+        <v>83.86487900000002</v>
       </c>
       <c r="N96">
-        <v>149.6534721333334</v>
+        <v>139.7684543333334</v>
       </c>
       <c r="O96">
-        <v>22.44802082</v>
+        <v>20.96526815</v>
       </c>
       <c r="P96">
-        <v>127.2054513133334</v>
+        <v>118.8031861833334</v>
       </c>
       <c r="Q96">
-        <v>190.9054513133333</v>
+        <v>182.5031861833334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.750463084078994</v>
+        <v>2.087823647866456</v>
       </c>
       <c r="T96">
-        <v>10.42550721771805</v>
+        <v>12.48876242960638</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.15</v>
       </c>
       <c r="W96">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.022894740620754</v>
+        <v>2.666591021175066</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1624504323933227</v>
+        <v>0.1624249797419058</v>
       </c>
       <c r="C97">
-        <v>458.8845734935546</v>
+        <v>446.9516372108246</v>
       </c>
       <c r="D97">
-        <v>1581.094573493555</v>
+        <v>1581.439637210825</v>
       </c>
       <c r="E97">
-        <v>429.7100000000002</v>
+        <v>441.9880000000002</v>
       </c>
       <c r="F97">
-        <v>1166.41</v>
+        <v>1178.688</v>
       </c>
       <c r="G97">
         <v>44.2</v>
@@ -9241,28 +9241,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M97">
-        <v>83.86487900000002</v>
+        <v>84.74766720000001</v>
       </c>
       <c r="N97">
-        <v>139.7684543333334</v>
+        <v>138.8856661333334</v>
       </c>
       <c r="O97">
-        <v>20.96526815</v>
+        <v>20.83284992</v>
       </c>
       <c r="P97">
-        <v>118.8031861833334</v>
+        <v>118.0528162133334</v>
       </c>
       <c r="Q97">
-        <v>182.5031861833334</v>
+        <v>181.7528162133333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.087823647866456</v>
+        <v>2.593864493547648</v>
       </c>
       <c r="T97">
-        <v>12.48876242960638</v>
+        <v>15.58364524743888</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.666591021175066</v>
+        <v>2.638814031371159</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1624249797419058</v>
+        <v>0.1623995270904889</v>
       </c>
       <c r="C98">
-        <v>446.9516372108249</v>
+        <v>435.0188515768446</v>
       </c>
       <c r="D98">
-        <v>1581.439637210825</v>
+        <v>1581.784851576844</v>
       </c>
       <c r="E98">
-        <v>441.9879999999999</v>
+        <v>454.266</v>
       </c>
       <c r="F98">
-        <v>1178.688</v>
+        <v>1190.966</v>
       </c>
       <c r="G98">
         <v>44.2</v>
@@ -9323,28 +9323,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M98">
-        <v>84.7476672</v>
+        <v>85.6304554</v>
       </c>
       <c r="N98">
-        <v>138.8856661333334</v>
+        <v>138.0028779333334</v>
       </c>
       <c r="O98">
-        <v>20.83284992000001</v>
+        <v>20.70043169000001</v>
       </c>
       <c r="P98">
-        <v>118.0528162133334</v>
+        <v>117.3024462433334</v>
       </c>
       <c r="Q98">
-        <v>181.7528162133334</v>
+        <v>181.0024462433334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.593864493547642</v>
+        <v>3.437265903016293</v>
       </c>
       <c r="T98">
-        <v>15.58364524743883</v>
+        <v>20.74178327715963</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.63881403137116</v>
+        <v>2.611609763006508</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1623995270904889</v>
+        <v>0.162374074439072</v>
       </c>
       <c r="C99">
-        <v>435.0188515768446</v>
+        <v>423.0862166902923</v>
       </c>
       <c r="D99">
-        <v>1581.784851576844</v>
+        <v>1582.130216690292</v>
       </c>
       <c r="E99">
-        <v>454.266</v>
+        <v>466.544</v>
       </c>
       <c r="F99">
-        <v>1190.966</v>
+        <v>1203.244</v>
       </c>
       <c r="G99">
         <v>44.2</v>
@@ -9405,28 +9405,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M99">
-        <v>85.6304554</v>
+        <v>86.5132436</v>
       </c>
       <c r="N99">
-        <v>138.0028779333334</v>
+        <v>137.1200897333334</v>
       </c>
       <c r="O99">
-        <v>20.70043169000001</v>
+        <v>20.56801346000001</v>
       </c>
       <c r="P99">
-        <v>117.3024462433334</v>
+        <v>116.5520762733334</v>
       </c>
       <c r="Q99">
-        <v>181.0024462433334</v>
+        <v>180.2520762733334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.437265903016293</v>
+        <v>5.124068721953594</v>
       </c>
       <c r="T99">
-        <v>20.74178327715963</v>
+        <v>31.05805933660123</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.611609763006508</v>
+        <v>2.584960683792156</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.162374074439072</v>
+        <v>0.1623486217876551</v>
       </c>
       <c r="C100">
-        <v>423.0862166902923</v>
+        <v>411.1537326499313</v>
       </c>
       <c r="D100">
-        <v>1582.130216690292</v>
+        <v>1582.475732649931</v>
       </c>
       <c r="E100">
-        <v>466.544</v>
+        <v>478.822</v>
       </c>
       <c r="F100">
-        <v>1203.244</v>
+        <v>1215.522</v>
       </c>
       <c r="G100">
         <v>44.2</v>
@@ -9487,28 +9487,28 @@
         <v>223.6333333333334</v>
       </c>
       <c r="M100">
-        <v>86.5132436</v>
+        <v>87.3960318</v>
       </c>
       <c r="N100">
-        <v>137.1200897333334</v>
+        <v>136.2373015333334</v>
       </c>
       <c r="O100">
-        <v>20.56801346000001</v>
+        <v>20.43559523000001</v>
       </c>
       <c r="P100">
-        <v>116.5520762733334</v>
+        <v>115.8017063033334</v>
       </c>
       <c r="Q100">
-        <v>180.2520762733334</v>
+        <v>179.5017063033334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.124068721953594</v>
+        <v>10.1844771787655</v>
       </c>
       <c r="T100">
-        <v>31.05805933660123</v>
+        <v>62.00688751492601</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.584960683792156</v>
+        <v>2.558849969814458</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1623486217876551</v>
-      </c>
-      <c r="C101">
-        <v>411.1537326499313</v>
-      </c>
-      <c r="D101">
-        <v>1582.475732649931</v>
-      </c>
-      <c r="E101">
-        <v>478.822</v>
-      </c>
-      <c r="F101">
-        <v>1215.522</v>
-      </c>
-      <c r="G101">
-        <v>44.2</v>
-      </c>
-      <c r="H101">
-        <v>491.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>287.3333333333334</v>
-      </c>
-      <c r="K101">
-        <v>63.7</v>
-      </c>
-      <c r="L101">
-        <v>223.6333333333334</v>
-      </c>
-      <c r="M101">
-        <v>87.3960318</v>
-      </c>
-      <c r="N101">
-        <v>136.2373015333334</v>
-      </c>
-      <c r="O101">
-        <v>20.43559523000001</v>
-      </c>
-      <c r="P101">
-        <v>115.8017063033334</v>
-      </c>
-      <c r="Q101">
-        <v>179.5017063033334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.1844771787655</v>
-      </c>
-      <c r="T101">
-        <v>62.00688751492601</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.061115</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.558849969814458</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
